--- a/Automotive Data Solutions/benchmark_shares_v3.xlsx
+++ b/Automotive Data Solutions/benchmark_shares_v3.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="195">
   <si>
     <t>This document was exported from Numbers.  Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
   </si>
@@ -109,7 +109,7 @@
     <t>https://www.cobaltinstitute.org/wp-content/uploads/2025/05/Cobalt-Market-Report-2024.pdf</t>
   </si>
   <si>
-    <t>Table 2 p.43 (2023: 78.6% - unchanged y-o-y). VERIFIED against full PDF 2026-07-15. Known internal inconsistency in the report itself: section 4.5 p.40 says total refined = 222kt with China at 131kt 'accounting for 79%', but 131/222 = 59%. Reconciliation: 131/0.786 = 167kt, i.e. the share denominator is the 'final refined products' universe excluding crude hydroxide (per the Fig 36 note on avoiding double-counting). The share table is self-consistent (sums to 99.9%) and stands.</t>
+    <t>Table 2 p.43 (2023: 78.6% - unchanged y-o-y). VERIFIED against full PDF 2026-07-15. Known internal inconsistency in the report itself: section 4.5 p.40 says total refined = 222kt with China at 131kt 'accounting for 79%', but 131/222 = 59%. Reconciliation: 131/0.786 = 167kt, i.e. the share denominator is the 'final refined products' universe excluding crude hydroxide (per the Fig 36 note on avoiding double-counting). The share table is self-consistent (sums to 99.9%) and stands. | GCMO 2026 p.162 corroborates: 'more than 75% of the market in 2025, a share that remains broadly unchanged.' IEA's cobalt data is credited to Benchmark Minerals Intelligence - same upstream as this table.</t>
   </si>
   <si>
     <t>Y</t>
@@ -151,6 +151,36 @@
     <t>AU</t>
   </si>
   <si>
+    <t>Refined cobalt production, all forms (metal + chemicals), share of world total — final refined products excl. crude hydroxide (double-count guard per CI convention)</t>
+  </si>
+  <si>
+    <t>https://www.cobaltinstitute.org/resource-category/market-report/</t>
+  </si>
+  <si>
+    <t>CI Cobalt Market Report 2025 (May 2026), Table 1 'Refined cobalt market share by country' p.16: CN 0.786 in 2025 (y-o-y -0.8pp). Data: Benchmark Mineral Intelligence Cobalt Forecast. ROW 3.0% inside the 100% -&gt; shares are of world total. SUPERSEDES the IEA GCMO annex 6-country rows @2025 (CN 75.6 by annex kt — universe difference); those DB rows deleted via one-time SQL (source=benchmark_iea_global_critical_mi, 810520, 2025). Source URL = CI market-report library page; direct 2025 PDF link TBD (report in hand, uploaded 2026-08-11).</t>
+  </si>
+  <si>
+    <t>CI Cobalt Market Report 2025 (May 2026), Table 1 'Refined cobalt market share by country' p.16: FI 0.066 in 2025 (y-o-y -0.4pp). Data: Benchmark Mineral Intelligence Cobalt Forecast. ROW 3.0% inside the 100% -&gt; shares are of world total. SUPERSEDES the IEA GCMO annex 6-country rows @2025 (CN 75.6 by annex kt — universe difference); those DB rows deleted via one-time SQL (source=benchmark_iea_global_critical_mi, 810520, 2025). Source URL = CI market-report library page; direct 2025 PDF link TBD (report in hand, uploaded 2026-08-11).</t>
+  </si>
+  <si>
+    <t>CI Cobalt Market Report 2025 (May 2026), Table 1 'Refined cobalt market share by country' p.16: JP 0.017 in 2025 (y-o-y -0.1pp). Data: Benchmark Mineral Intelligence Cobalt Forecast. ROW 3.0% inside the 100% -&gt; shares are of world total. SUPERSEDES the IEA GCMO annex 6-country rows @2025 (CN 75.6 by annex kt — universe difference); those DB rows deleted via one-time SQL (source=benchmark_iea_global_critical_mi, 810520, 2025). Source URL = CI market-report library page; direct 2025 PDF link TBD (report in hand, uploaded 2026-08-11).</t>
+  </si>
+  <si>
+    <t>CI Cobalt Market Report 2025 (May 2026), Table 1 'Refined cobalt market share by country' p.16: ID 0.032 in 2025 (y-o-y +1.5pp). Data: Benchmark Mineral Intelligence Cobalt Forecast. ROW 3.0% inside the 100% -&gt; shares are of world total. SUPERSEDES the IEA GCMO annex 6-country rows @2025 (CN 75.6 by annex kt — universe difference); those DB rows deleted via one-time SQL (source=benchmark_iea_global_critical_mi, 810520, 2025). Source URL = CI market-report library page; direct 2025 PDF link TBD (report in hand, uploaded 2026-08-11).</t>
+  </si>
+  <si>
+    <t>CI Cobalt Market Report 2025 (May 2026), Table 1 'Refined cobalt market share by country' p.16: CA 0.03 in 2025 (y-o-y +0.3pp). Data: Benchmark Mineral Intelligence Cobalt Forecast. ROW 3.0% inside the 100% -&gt; shares are of world total. SUPERSEDES the IEA GCMO annex 6-country rows @2025 (CN 75.6 by annex kt — universe difference); those DB rows deleted via one-time SQL (source=benchmark_iea_global_critical_mi, 810520, 2025). Source URL = CI market-report library page; direct 2025 PDF link TBD (report in hand, uploaded 2026-08-11).</t>
+  </si>
+  <si>
+    <t>CI Cobalt Market Report 2025 (May 2026), Table 1 'Refined cobalt market share by country' p.16: NO 0.013 in 2025 (y-o-y flat). Data: Benchmark Mineral Intelligence Cobalt Forecast. ROW 3.0% inside the 100% -&gt; shares are of world total. SUPERSEDES the IEA GCMO annex 6-country rows @2025 (CN 75.6 by annex kt — universe difference); those DB rows deleted via one-time SQL (source=benchmark_iea_global_critical_mi, 810520, 2025). Source URL = CI market-report library page; direct 2025 PDF link TBD (report in hand, uploaded 2026-08-11).</t>
+  </si>
+  <si>
+    <t>CI Cobalt Market Report 2025 (May 2026), Table 1 'Refined cobalt market share by country' p.16: MG 0.019 in 2025 (y-o-y +0.1pp). Data: Benchmark Mineral Intelligence Cobalt Forecast. ROW 3.0% inside the 100% -&gt; shares are of world total. SUPERSEDES the IEA GCMO annex 6-country rows @2025 (CN 75.6 by annex kt — universe difference); those DB rows deleted via one-time SQL (source=benchmark_iea_global_critical_mi, 810520, 2025). Source URL = CI market-report library page; direct 2025 PDF link TBD (report in hand, uploaded 2026-08-11).</t>
+  </si>
+  <si>
+    <t>CI Cobalt Market Report 2025 (May 2026), Table 1 'Refined cobalt market share by country' p.16: AU 0.01 in 2025 (y-o-y -0.3pp). Data: Benchmark Mineral Intelligence Cobalt Forecast. ROW 3.0% inside the 100% -&gt; shares are of world total. SUPERSEDES the IEA GCMO annex 6-country rows @2025 (CN 75.6 by annex kt — universe difference); those DB rows deleted via one-time SQL (source=benchmark_iea_global_critical_mi, 810520, 2025). Source URL = CI market-report library page; direct 2025 PDF link TBD (report in hand, uploaded 2026-08-11).</t>
+  </si>
+  <si>
     <t>2822;282200</t>
   </si>
   <si>
@@ -160,10 +190,16 @@
     <t>Mined cobalt production used as PROXY for intermediates (crude hydroxide / MHP) - per-country intermediates production is not published; mined output converts to hydroxide (CD) or MHP (ID) largely in-country</t>
   </si>
   <si>
-    <t>VERIFIED: section 4.1 p.28 'DRC... 76% of mined output'; Fig 29 p.38 shows 192kt of 254kt. Supporting: USGS (Springer 2024) - crude cobalt hydroxide 'produced almost exclusively in the DRC' (2022). Note: DRC majors (CMOC/Glencore/ERG) = 85% of DRC exports (p.28).</t>
-  </si>
-  <si>
-    <t>VERIFIED: p.38 'from 2% of global cobalt in 2021 to 12% in 2024'; 30kt mined, +82% y-o-y; Fig 47 p.66 shows 12%. ID output is 89% MHP / 11% matte (Fig 31 p.39).</t>
+    <t>IEA (Global Critical Minerals Outlook 2026, Annex)</t>
+  </si>
+  <si>
+    <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+  </si>
+  <si>
+    <t>GCMO 2026 Annex p.357 'Cobalt supply — Mining' 2025: DRC 210 kt / World 320 kt (incl. RoW 39 kt) = 0.656. Supersedes prose-derived 0.667 ('two-thirds', p.157). Caveat: DRC 2025-26 figures reflect SOLD supply under the ARECOMS quota (p.157 note). Basis unchanged: mined as proxy for intermediates (p.161 intermediates figure corroborates).</t>
+  </si>
+  <si>
+    <t>GCMO 2026 Annex p.357 'Cobalt supply — Mining' 2025: Indonesia 48 kt / World 320 kt = 0.150 (exact; matches p.156 'approximately 15% in 2025').</t>
   </si>
   <si>
     <t>2833;283329</t>
@@ -190,63 +226,108 @@
     <t>Lithium chemicals production (carbonate+hydroxide combined), kt Li content</t>
   </si>
   <si>
+    <t>GCMO 2026 Annex p.351 'Lithium supply — Chemicals' 2025: China 235 kt Li / World 319 kt (incl. RoW 5 kt) = 0.737.</t>
+  </si>
+  <si>
+    <t>CL</t>
+  </si>
+  <si>
+    <t>GCMO 2026 Annex p.351 'Lithium supply — Chemicals' 2025: Chile 52 kt Li / World 319 kt (incl. RoW 5 kt) = 0.163.</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>GCMO 2026 Annex p.351 'Lithium supply — Chemicals' 2025: Argentina 16 kt Li / World 319 kt (incl. RoW 5 kt) = 0.05.</t>
+  </si>
+  <si>
+    <t>GCMO 2026 Annex p.351 'Lithium supply — Chemicals' 2025: Australia 6 kt Li / World 319 kt (incl. RoW 5 kt) = 0.019.</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>Lithium chemicals production (carbonate, hydroxide, sulphates, chlorides; excl. reprocessing), share of world total incl. rest-of-world</t>
+  </si>
+  <si>
+    <t>GCMO 2026 Annex p.351 'Lithium supply — Chemicals' 2025: Germany 3 kt Li / World 319 kt (incl. RoW 5 kt) = 0.009.</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>GCMO 2026 Annex p.351 'Lithium supply — Chemicals' 2025: United States 1 kt Li / World 319 kt (incl. RoW 5 kt) = 0.003.</t>
+  </si>
+  <si>
+    <t>Nickel</t>
+  </si>
+  <si>
+    <t>7502;750210</t>
+  </si>
+  <si>
+    <t>Refined nickel production incl. class II/NPI and intermediates converted in-country, kt Ni</t>
+  </si>
+  <si>
+    <t>GCMO 2026 Annex p.354 'Nickel supply — Refining' 2025: Indonesia 1681 kt Ni / World 3729 kt (incl. RoW 367 kt) = 0.451. Refining incl. metal/oxide/NPI/ferronickel/sulphate, excl. intermediates (annex note).</t>
+  </si>
+  <si>
+    <t>Refined nickel production incl. class II/NPI, kt Ni</t>
+  </si>
+  <si>
+    <t>GCMO 2026 Annex p.354 'Nickel supply — Refining' 2025: China 1160 kt Ni / World 3729 kt (incl. RoW 367 kt) = 0.311. Refining incl. metal/oxide/NPI/ferronickel/sulphate, excl. intermediates (annex note).</t>
+  </si>
+  <si>
+    <t>RU</t>
+  </si>
+  <si>
+    <t>GCMO 2026 Annex p.354 'Nickel supply — Refining' 2025: Russia 123 kt Ni / World 3729 kt (incl. RoW 367 kt) = 0.033. Refining incl. metal/oxide/NPI/ferronickel/sulphate, excl. intermediates (annex note).</t>
+  </si>
+  <si>
+    <t>GCMO 2026 Annex p.354 'Nickel supply — Refining' 2025: Canada 125 kt Ni / World 3729 kt (incl. RoW 367 kt) = 0.034. Refining incl. metal/oxide/NPI/ferronickel/sulphate, excl. intermediates (annex note).</t>
+  </si>
+  <si>
     <t>IEA (Critical Minerals Data Explorer, GCMO 2025 base case)</t>
   </si>
   <si>
     <t>https://www.iea.org/data-and-statistics/data-tools/critical-minerals-data-explorer</t>
   </si>
   <si>
-    <t>CN 169.68 of total 241.61. NOTE: combined carbonate+hydroxide — CN share differs slightly by chemical (higher in hydroxide conversion); combined is best available. IEA CM Data Explorer sheet '2 Total supply', 2024 base-case actuals; share = country/Total (full-universe denominator). CC-BY 4.0.</t>
-  </si>
-  <si>
-    <t>CL</t>
-  </si>
-  <si>
-    <t>CL 49.27 of 241.61 (carbonate, Atacama). IEA CM Data Explorer sheet '2 Total supply', 2024 base-case actuals; share = country/Total (full-universe denominator). CC-BY 4.0.</t>
-  </si>
-  <si>
-    <t>AR</t>
-  </si>
-  <si>
-    <t>AR 13.18 of 241.61. IEA CM Data Explorer sheet '2 Total supply', 2024 base-case actuals; share = country/Total (full-universe denominator). CC-BY 4.0.</t>
-  </si>
-  <si>
-    <t>AU 4.33 of 241.61 (Kwinana/Kemerton — Kemerton idled Feb-2026, expect share to fall). IEA CM Data Explorer sheet '2 Total supply', 2024 base-case actuals; share = country/Total (full-universe denominator). CC-BY 4.0.</t>
-  </si>
-  <si>
-    <t>Nickel</t>
-  </si>
-  <si>
-    <t>7502;750210</t>
-  </si>
-  <si>
-    <t>Refined nickel production incl. class II/NPI and intermediates converted in-country, kt Ni</t>
-  </si>
-  <si>
-    <t>ID 1493.2 of total 3483.7. BASIS CAUTION: IEA 'refining' includes NPI/class II — broader than LME-grade class I. IEA CM Data Explorer sheet '2 Total supply', 2024 base-case actuals; share = country/Total (full-universe denominator). CC-BY 4.0.</t>
-  </si>
-  <si>
-    <t>Refined nickel production incl. class II/NPI, kt Ni</t>
-  </si>
-  <si>
-    <t>CN 1091.1 of 3483.7. Same basis caution. IEA CM Data Explorer sheet '2 Total supply', 2024 base-case actuals; share = country/Total (full-universe denominator). CC-BY 4.0.</t>
-  </si>
-  <si>
-    <t>RU</t>
-  </si>
-  <si>
-    <t>RU 126 of 3483.7 (Norilsk class I). IEA CM Data Explorer sheet '2 Total supply', 2024 base-case actuals; share = country/Total (full-universe denominator). CC-BY 4.0.</t>
-  </si>
-  <si>
-    <t>CA 113.1 of 3483.7. IEA CM Data Explorer sheet '2 Total supply', 2024 base-case actuals; share = country/Total (full-universe denominator). CC-BY 4.0.</t>
-  </si>
-  <si>
     <t>AU 80 of 3483.7 — pre-C&amp;M wave; expect down. IEA CM Data Explorer sheet '2 Total supply', 2024 base-case actuals; share = country/Total (full-universe denominator). CC-BY 4.0.</t>
   </si>
   <si>
     <t>FI 62 of 3483.7 (Harjavalta). IEA CM Data Explorer sheet '2 Total supply', 2024 base-case actuals; share = country/Total (full-universe denominator). CC-BY 4.0.</t>
   </si>
   <si>
+    <t>Refined nickel production (metal, oxide, NPI, ferronickel, sulphate; excl. intermediates), share of world total incl. rest-of-world</t>
+  </si>
+  <si>
+    <t>GCMO 2026 Annex p.354 'Nickel supply — Refining' 2025: Japan 108 kt Ni / World 3729 kt (incl. RoW 367 kt) = 0.029. Refining incl. metal/oxide/NPI/ferronickel/sulphate, excl. intermediates (annex note).</t>
+  </si>
+  <si>
+    <t>GCMO 2026 Annex p.354 'Nickel supply — Refining' 2025: Norway 100 kt Ni / World 3729 kt (incl. RoW 367 kt) = 0.027. Refining incl. metal/oxide/NPI/ferronickel/sulphate, excl. intermediates (annex note).</t>
+  </si>
+  <si>
+    <t>BR</t>
+  </si>
+  <si>
+    <t>GCMO 2026 Annex p.354 'Nickel supply — Refining' 2025: Brazil 64 kt Ni / World 3729 kt (incl. RoW 367 kt) = 0.017. Refining incl. metal/oxide/NPI/ferronickel/sulphate, excl. intermediates (annex note).</t>
+  </si>
+  <si>
+    <t>283324</t>
+  </si>
+  <si>
+    <t>Battery-grade nickel sulphate (NiSO4) production, share of world total incl. rest-of-world (~15%: JP/FI/BE plants, unnamed in source)</t>
+  </si>
+  <si>
+    <t>IEA (Global Critical Minerals Outlook 2026)</t>
+  </si>
+  <si>
+    <t>GCMO 2026 p.151: 'China remains the dominant battery-grade nickel sulphate producer, accounting for 75% of production' (2025, PRODUCTION basis — not the p.154 capacity chart). Stage-ladder coverage memo finding 1; fills the known largest invisible understatement (nickel published 77.55 off ID ore).</t>
+  </si>
+  <si>
+    <t>GCMO 2026 p.151: 'Indonesia produces only 10% of global nickel sulphate and continues to export intermediate products such as MHP to China for further processing' (2025). 75 kt of mattes exported to China in 2025 (~25% of supply).</t>
+  </si>
+  <si>
     <t>Natural Graphite</t>
   </si>
   <si>
@@ -256,10 +337,28 @@
     <t>Battery-grade (anode) graphite — COMBINED natural-spherical + synthetic anode, converged/shared stage, kt</t>
   </si>
   <si>
-    <t>COMBINED-ANODE BASIS (decision 2026-07-19): battery-grade graphite is a converged market — Natural &amp; Synthetic materials both carry this anode concentration at battery_grade by design; their UPSTREAM stages stay material-specific (natural rides ore flake, synthetic its needle-coke feedstock). CN 1794.8 of 1875.3 (~95.7%); CN dominates both spherical (~100%) and synthetic graphitization. IEA CM Data Explorer 'Total supply' sheet, 2024 base-case; share=country/Total (full-universe denominator). CC-BY 4.0.</t>
-  </si>
-  <si>
-    <t>COMBINED-ANODE BASIS (2026-07-19, shared anode stage with Synthetic Graphite). JP 44.97 of 1875.3, mostly synthetic chain. IEA CM Data Explorer 'Total supply' sheet, 2024 base-case; share=country/Total (full-universe denominator). CC-BY 4.0.</t>
+    <t>GCMO 2026 Annex p.360 'Graphite supply — Refined battery-grade supply' 2025: China 2139 kt / World 2266 kt (incl. RoW 3 kt) = 0.944. Combined natural spherical + synthetic anode (annex note; shared-stage decision 2026-07-19).</t>
+  </si>
+  <si>
+    <t>GCMO 2026 Annex p.360 'Graphite supply — Refined battery-grade supply' 2025: Japan 68 kt / World 2266 kt (incl. RoW 3 kt) = 0.03. Combined natural spherical + synthetic anode (annex note; shared-stage decision 2026-07-19).</t>
+  </si>
+  <si>
+    <t>Battery-grade (anode) graphite — COMBINED natural spherical + synthetic anode production, share of world total incl. rest-of-world</t>
+  </si>
+  <si>
+    <t>GCMO 2026 Annex p.360 'Graphite supply — Refined battery-grade supply' 2025: Indonesia 32 kt / World 2266 kt (incl. RoW 3 kt) = 0.014. Combined natural spherical + synthetic anode (annex note; shared-stage decision 2026-07-19).</t>
+  </si>
+  <si>
+    <t>GCMO 2026 Annex p.360 'Graphite supply — Refined battery-grade supply' 2025: United States 13 kt / World 2266 kt (incl. RoW 3 kt) = 0.006. Combined natural spherical + synthetic anode (annex note; shared-stage decision 2026-07-19).</t>
+  </si>
+  <si>
+    <t>KR</t>
+  </si>
+  <si>
+    <t>GCMO 2026 Annex p.360 'Graphite supply — Refined battery-grade supply' 2025: Korea 5 kt / World 2266 kt (incl. RoW 3 kt) = 0.002. Combined natural spherical + synthetic anode (annex note; shared-stage decision 2026-07-19).</t>
+  </si>
+  <si>
+    <t>GCMO 2026 Annex p.360 'Graphite supply — Refined battery-grade supply' 2025: Germany 5 kt / World 2266 kt (incl. RoW 3 kt) = 0.002. Combined natural spherical + synthetic anode (annex note; shared-stage decision 2026-07-19).</t>
   </si>
   <si>
     <t>Synthetic Graphite</t>
@@ -268,12 +367,6 @@
     <t>380110</t>
   </si>
   <si>
-    <t>COMBINED-ANODE BASIS (2026-07-19): same converged anode series as Natural Graphite; both materials carry it at battery_grade by design (380110 used as the anode-market reference node). CN ~95.7%. IEA CM Data Explorer 'Total supply' sheet, 2024 base-case; share=country/Total (full-universe denominator). CC-BY 4.0.</t>
-  </si>
-  <si>
-    <t>COMBINED-ANODE BASIS (2026-07-19, shared anode stage with Natural Graphite). JP synthetic chain (Resonac / ex-Showa Denko, Tokai). IEA CM Data Explorer 'Total supply' sheet, 2024 base-case; share=country/Total (full-universe denominator). CC-BY 4.0.</t>
-  </si>
-  <si>
     <t>Rare Earth Elements</t>
   </si>
   <si>
@@ -283,7 +376,7 @@
     <t>Magnet rare earth (Nd,Pr,Dy,Tb) REFINING/separation output, kt REO</t>
   </si>
   <si>
-    <t>CN 73.76 of total 80.81. BASIS: magnet REE only (narrower than total REO; total-REO refining CN similar ~85-90%). STAGE (2026-07-19 reclassification): 284690 flipped intermediate→battery_grade, so BOTH 2846 &amp; 284690 now resolve to battery_grade and the row loads to ONE stage (loader dedup keeps 6-digit 284690) — no cross-stage smear. Separated magnet-REE oxides = last specialty-chemical stage before NdFeB magnets = our battery_grade, by parallel with lithium chemicals. IEA CM Data Explorer sheet '2 Total supply', 2024 base-case; share=country/Total (full-universe denominator). CC-BY 4.0.</t>
+    <t>GCMO 2026 Annex p.363 'Rare earth elements supply — Refining' 2025: China 75 kt REE / World 89 kt (incl. RoW 3 kt) = 0.843. Magnet REEs only (Nd/Pr/Dy/Tb).</t>
   </si>
   <si>
     <t>MY</t>
@@ -292,13 +385,52 @@
     <t>Magnet rare earth refining/separation, kt REO</t>
   </si>
   <si>
-    <t>MY 3.63 of 80.81 (Lynas Kuantan). Loads to battery_grade (284690 reclassified 2026-07-19; see CN row). IEA CM Data Explorer sheet '2 Total supply', 2024 base-case; share=country/Total (full-universe denominator). CC-BY 4.0.</t>
-  </si>
-  <si>
-    <t>US</t>
-  </si>
-  <si>
-    <t>US 0.96 of 80.81 (MP Mountain Pass). Loads to battery_grade (284690 reclassified 2026-07-19; see CN row). IEA CM Data Explorer sheet '2 Total supply', 2024 base-case; share=country/Total (full-universe denominator). CC-BY 4.0.</t>
+    <t>GCMO 2026 Annex p.363 'Rare earth elements supply — Refining' 2025: Malaysia 5 kt REE / World 89 kt (incl. RoW 3 kt) = 0.056. Magnet REEs only (Nd/Pr/Dy/Tb).</t>
+  </si>
+  <si>
+    <t>GCMO 2026 Annex p.363 'Rare earth elements supply — Refining' 2025: United States 5 kt REE / World 89 kt (incl. RoW 3 kt) = 0.056. Magnet REEs only (Nd/Pr/Dy/Tb).</t>
+  </si>
+  <si>
+    <t>FR</t>
+  </si>
+  <si>
+    <t>Magnet rare earth (Nd,Pr,Dy,Tb) refining/separation, kt REE, share of world total incl. rest-of-world</t>
+  </si>
+  <si>
+    <t>GCMO 2026 Annex p.363 'Rare earth elements supply — Refining' 2025: France 1 kt REE / World 89 kt (incl. RoW 3 kt) = 0.011. Magnet REEs only (Nd/Pr/Dy/Tb).</t>
+  </si>
+  <si>
+    <t>VN</t>
+  </si>
+  <si>
+    <t>GCMO 2026 Annex p.363 'Rare earth elements supply — Refining' 2025: Viet Nam 1 kt REE / World 89 kt (incl. RoW 3 kt) = 0.011. Magnet REEs only (Nd/Pr/Dy/Tb).</t>
+  </si>
+  <si>
+    <t>280530</t>
+  </si>
+  <si>
+    <t>Magnet rare earth METAL-MAKING (unwrought RE metals, HS 280530) — NdPr metal distribution used as proxy for aggregate magnet-metal stage (Dy/Tb volumes negligible)</t>
+  </si>
+  <si>
+    <t>Rare Earth Exchanges (2025 processing review)</t>
+  </si>
+  <si>
+    <t>https://rareearthexchanges.com/news/rare-earth-processing-2025-global-capacity-and-key-players/</t>
+  </si>
+  <si>
+    <t>Aggregate refined stage fill (2026-08-10, stage-ladder coverage memo finding 2, Nicole approved): reuses the audited NdPr metal distribution already in this workbook (Neodymium/Praseodymium rows, Rare Earth Exchanges 2025 processing shares) — CN = 0.89. Dy/Tb metal (Mining.com rows) is CN .98/MY .02 but tonnage-negligible vs NdPr. Ladder note: 280530 metal physically FOLLOWS 284690 oxide separation; mapped 'refined' per the 2026-07 ladder decision — stage-max is order-independent; A6 documents it.</t>
+  </si>
+  <si>
+    <t>Aggregate refined stage fill (2026-08-10, stage-ladder coverage memo finding 2, Nicole approved): reuses the audited NdPr metal distribution already in this workbook (Neodymium/Praseodymium rows, Rare Earth Exchanges 2025 processing shares) — MY = 0.07. Dy/Tb metal (Mining.com rows) is CN .98/MY .02 but tonnage-negligible vs NdPr. Ladder note: 280530 metal physically FOLLOWS 284690 oxide separation; mapped 'refined' per the 2026-07 ladder decision — stage-max is order-independent; A6 documents it.</t>
+  </si>
+  <si>
+    <t>Aggregate refined stage fill (2026-08-10, stage-ladder coverage memo finding 2, Nicole approved): reuses the audited NdPr metal distribution already in this workbook (Neodymium/Praseodymium rows, Rare Earth Exchanges 2025 processing shares) — US = 0.02. Dy/Tb metal (Mining.com rows) is CN .98/MY .02 but tonnage-negligible vs NdPr. Ladder note: 280530 metal physically FOLLOWS 284690 oxide separation; mapped 'refined' per the 2026-07 ladder decision — stage-max is order-independent; A6 documents it.</t>
+  </si>
+  <si>
+    <t>EE</t>
+  </si>
+  <si>
+    <t>Aggregate refined stage fill (2026-08-10, stage-ladder coverage memo finding 2, Nicole approved): reuses the audited NdPr metal distribution already in this workbook (Neodymium/Praseodymium rows, Rare Earth Exchanges 2025 processing shares) — EE = 0.01. Dy/Tb metal (Mining.com rows) is CN .98/MY .02 but tonnage-negligible vs NdPr. Ladder note: 280530 metal physically FOLLOWS 284690 oxide separation; mapped 'refined' per the 2026-07 ladder decision — stage-max is order-independent; A6 documents it.</t>
   </si>
   <si>
     <t>Manganese</t>
@@ -310,12 +442,6 @@
     <t>Battery-grade manganese sulphate (HPMSM) production, 2025, share of world. China share IEA-stated (&gt;95%); Japan+Belgium are the only non-China refineries (residual split estimated).</t>
   </si>
   <si>
-    <t>IEA (Global Critical Minerals Outlook 2026)</t>
-  </si>
-  <si>
-    <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
-  </si>
-  <si>
     <t>GCMO 2026 p.188: 'China producing over 95% of global supplies in 2025.' Only two operating battery-grade Mn sulphate refineries outside China (Japan, Belgium). Manganese demand still steel-dominated; battery-grade is the emerging chokepoint. CC-BY 4.0.</t>
   </si>
   <si>
@@ -352,18 +478,9 @@
     <t>Neodymium</t>
   </si>
   <si>
-    <t>280530</t>
-  </si>
-  <si>
     <t>Separated NdPr oxide production (refined stage 280530), share of world total</t>
   </si>
   <si>
-    <t>Rare Earth Exchanges (2025 processing review)</t>
-  </si>
-  <si>
-    <t>https://rareearthexchanges.com/news/rare-earth-processing-2025-global-capacity-and-key-players/</t>
-  </si>
-  <si>
     <t>China ~90% of global separation capacity (2025). UNVERIFIED - added 2026-07-26 to close the conc=0 gap; check share vs a volume-based source before auditing.</t>
   </si>
   <si>
@@ -373,9 +490,6 @@
     <t>MP Materials 1.3kt NdPr oxide (2024), ramping. UNVERIFIED.</t>
   </si>
   <si>
-    <t>EE</t>
-  </si>
-  <si>
     <t>Neo Silmet - EU's only commercial separator. UNVERIFIED.</t>
   </si>
   <si>
@@ -428,9 +542,6 @@
   </si>
   <si>
     <t>Umicore incl. recycling. UNVERIFIED.</t>
-  </si>
-  <si>
-    <t>DE</t>
   </si>
   <si>
     <t>BENCHMARK SHARES WORKBOOK</t>
@@ -660,7 +771,9 @@
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin">
+        <color indexed="13"/>
+      </right>
       <top/>
       <bottom style="thin">
         <color indexed="13"/>
@@ -669,9 +782,7 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color indexed="13"/>
-      </right>
+      <right/>
       <top/>
       <bottom style="thin">
         <color indexed="13"/>
@@ -712,7 +823,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -740,7 +851,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -749,7 +860,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -776,17 +887,17 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
@@ -834,6 +945,18 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
@@ -1932,7 +2055,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -2047,16 +2170,19 @@
       <c r="D12" t="s" s="5">
         <v>6</v>
       </c>
-      <c r="E12" s="24"/>
-    </row>
-    <row r="13">
+      <c r="E12" s="21"/>
+    </row>
+    <row r="13" ht="13" customHeight="1">
+      <c r="A13" s="7"/>
       <c r="B13" t="s" s="3">
         <v>8</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
-    </row>
-    <row r="14">
+      <c r="E13" s="9"/>
+    </row>
+    <row r="14" ht="13" customHeight="1">
+      <c r="A14" s="20"/>
       <c r="B14" s="4"/>
       <c r="C14" t="s" s="4">
         <v>5</v>
@@ -2064,6 +2190,7 @@
       <c r="D14" t="s" s="5">
         <v>8</v>
       </c>
+      <c r="E14" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2073,7 +2200,8 @@
   <hyperlinks>
     <hyperlink ref="D10" location="'Export Summary'!R1C1" tooltip="" display="Export Summary"/>
     <hyperlink ref="D10" location="'Benchmark Shares'!R1C1" tooltip="" display="Benchmark Shares"/>
-    <hyperlink ref="D12" location="'Field Guide'!R1C1" tooltip="" display="Field Guide"/>
+    <hyperlink ref="D12" location="'Benchmark Shares'!R1C1" tooltip="" display="Benchmark Shares"/>
+    <hyperlink ref="D14" location="'Field Guide'!R1C1" tooltip="" display="Field Guide"/>
     <hyperlink ref="D12" location="'Benchmark Shares'!R1C1" tooltip="" display="Benchmark Shares"/>
     <hyperlink ref="D14" location="'Field Guide'!R1C1" tooltip="" display="Field Guide"/>
   </hyperlinks>
@@ -2087,7 +2215,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="10" style="25" customWidth="1"/>
@@ -2392,384 +2520,384 @@
       </c>
     </row>
     <row r="10" ht="52.55" customHeight="1">
-      <c r="A10" t="s" s="31">
+      <c r="A10" t="s" s="33">
         <v>20</v>
       </c>
-      <c r="B10" t="s" s="31">
+      <c r="B10" t="s" s="34">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s" s="34">
+        <v>22</v>
+      </c>
+      <c r="D10" s="35">
+        <v>0.786</v>
+      </c>
+      <c r="E10" s="35">
+        <v>2025</v>
+      </c>
+      <c r="F10" t="s" s="34">
         <v>40</v>
       </c>
-      <c r="C10" t="s" s="31">
+      <c r="G10" t="s" s="34">
+        <v>24</v>
+      </c>
+      <c r="H10" t="s" s="34">
         <v>41</v>
       </c>
-      <c r="D10" s="32">
-        <v>0.76</v>
-      </c>
-      <c r="E10" s="32">
-        <v>2024</v>
-      </c>
-      <c r="F10" t="s" s="31">
+      <c r="I10" t="s" s="34">
         <v>42</v>
       </c>
-      <c r="G10" t="s" s="31">
+      <c r="J10" t="s" s="36">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" ht="52.55" customHeight="1">
+      <c r="A11" t="s" s="37">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s" s="38">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s" s="38">
+        <v>28</v>
+      </c>
+      <c r="D11" s="39">
+        <v>0.066</v>
+      </c>
+      <c r="E11" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F11" t="s" s="38">
+        <v>40</v>
+      </c>
+      <c r="G11" t="s" s="38">
         <v>24</v>
       </c>
-      <c r="H10" t="s" s="31">
-        <v>25</v>
-      </c>
-      <c r="I10" t="s" s="31">
+      <c r="H11" t="s" s="38">
+        <v>41</v>
+      </c>
+      <c r="I11" t="s" s="38">
         <v>43</v>
       </c>
-      <c r="J10" t="s" s="31">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" ht="52.55" customHeight="1">
-      <c r="A11" t="s" s="31">
+      <c r="J11" t="s" s="40">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" ht="65.55" customHeight="1">
+      <c r="A12" t="s" s="37">
         <v>20</v>
       </c>
-      <c r="B11" t="s" s="31">
+      <c r="B12" t="s" s="38">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s" s="38">
+        <v>32</v>
+      </c>
+      <c r="D12" s="39">
+        <v>0.017</v>
+      </c>
+      <c r="E12" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F12" t="s" s="38">
         <v>40</v>
       </c>
-      <c r="C11" t="s" s="31">
+      <c r="G12" t="s" s="38">
+        <v>24</v>
+      </c>
+      <c r="H12" t="s" s="38">
+        <v>41</v>
+      </c>
+      <c r="I12" t="s" s="38">
+        <v>44</v>
+      </c>
+      <c r="J12" t="s" s="40">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" ht="13.55" customHeight="1">
+      <c r="A13" t="s" s="37">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s" s="38">
+        <v>21</v>
+      </c>
+      <c r="C13" t="s" s="38">
         <v>36</v>
       </c>
-      <c r="D11" s="32">
-        <v>0.12</v>
-      </c>
-      <c r="E11" s="32">
-        <v>2024</v>
-      </c>
-      <c r="F11" t="s" s="31">
-        <v>42</v>
-      </c>
-      <c r="G11" t="s" s="31">
+      <c r="D13" s="39">
+        <v>0.032</v>
+      </c>
+      <c r="E13" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F13" t="s" s="38">
+        <v>40</v>
+      </c>
+      <c r="G13" t="s" s="38">
         <v>24</v>
       </c>
-      <c r="H11" t="s" s="31">
-        <v>25</v>
-      </c>
-      <c r="I11" t="s" s="31">
-        <v>44</v>
-      </c>
-      <c r="J11" t="s" s="31">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" ht="65.55" customHeight="1">
-      <c r="A12" t="s" s="31">
-        <v>20</v>
-      </c>
-      <c r="B12" t="s" s="31">
+      <c r="H13" t="s" s="38">
+        <v>41</v>
+      </c>
+      <c r="I13" t="s" s="38">
         <v>45</v>
       </c>
-      <c r="C12" t="s" s="31">
-        <v>22</v>
-      </c>
-      <c r="D12" s="32">
-        <v>0.85</v>
-      </c>
-      <c r="E12" s="32">
-        <v>2022</v>
-      </c>
-      <c r="F12" t="s" s="31">
-        <v>46</v>
-      </c>
-      <c r="G12" t="s" s="31">
-        <v>47</v>
-      </c>
-      <c r="H12" t="s" s="31">
-        <v>48</v>
-      </c>
-      <c r="I12" t="s" s="31">
-        <v>49</v>
-      </c>
-      <c r="J12" t="s" s="31">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" ht="13.55" customHeight="1">
-      <c r="A13" t="s" s="33">
-        <v>50</v>
-      </c>
-      <c r="B13" t="s" s="34">
-        <v>51</v>
-      </c>
-      <c r="C13" t="s" s="34">
-        <v>22</v>
-      </c>
-      <c r="D13" s="35">
-        <v>0.702</v>
-      </c>
-      <c r="E13" s="35">
-        <v>2024</v>
-      </c>
-      <c r="F13" t="s" s="34">
-        <v>52</v>
-      </c>
-      <c r="G13" t="s" s="34">
-        <v>53</v>
-      </c>
-      <c r="H13" t="s" s="34">
-        <v>54</v>
-      </c>
-      <c r="I13" t="s" s="36">
-        <v>55</v>
-      </c>
-      <c r="J13" t="s" s="31">
+      <c r="J13" t="s" s="40">
         <v>27</v>
       </c>
     </row>
     <row r="14" ht="13.55" customHeight="1">
       <c r="A14" t="s" s="37">
+        <v>20</v>
+      </c>
+      <c r="B14" t="s" s="38">
+        <v>21</v>
+      </c>
+      <c r="C14" t="s" s="38">
+        <v>30</v>
+      </c>
+      <c r="D14" s="39">
+        <v>0.03</v>
+      </c>
+      <c r="E14" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F14" t="s" s="38">
+        <v>40</v>
+      </c>
+      <c r="G14" t="s" s="38">
+        <v>24</v>
+      </c>
+      <c r="H14" t="s" s="38">
+        <v>41</v>
+      </c>
+      <c r="I14" t="s" s="38">
+        <v>46</v>
+      </c>
+      <c r="J14" t="s" s="40">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" ht="13.55" customHeight="1">
+      <c r="A15" t="s" s="41">
+        <v>20</v>
+      </c>
+      <c r="B15" t="s" s="42">
+        <v>21</v>
+      </c>
+      <c r="C15" t="s" s="42">
+        <v>38</v>
+      </c>
+      <c r="D15" s="43">
+        <v>0.013</v>
+      </c>
+      <c r="E15" s="43">
+        <v>2025</v>
+      </c>
+      <c r="F15" t="s" s="42">
+        <v>40</v>
+      </c>
+      <c r="G15" t="s" s="42">
+        <v>24</v>
+      </c>
+      <c r="H15" t="s" s="42">
+        <v>41</v>
+      </c>
+      <c r="I15" t="s" s="42">
+        <v>47</v>
+      </c>
+      <c r="J15" t="s" s="44">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" ht="13.55" customHeight="1">
+      <c r="A16" t="s" s="33">
+        <v>20</v>
+      </c>
+      <c r="B16" t="s" s="34">
+        <v>21</v>
+      </c>
+      <c r="C16" t="s" s="34">
+        <v>34</v>
+      </c>
+      <c r="D16" s="35">
+        <v>0.019</v>
+      </c>
+      <c r="E16" s="35">
+        <v>2025</v>
+      </c>
+      <c r="F16" t="s" s="34">
+        <v>40</v>
+      </c>
+      <c r="G16" t="s" s="34">
+        <v>24</v>
+      </c>
+      <c r="H16" t="s" s="34">
+        <v>41</v>
+      </c>
+      <c r="I16" t="s" s="34">
+        <v>48</v>
+      </c>
+      <c r="J16" t="s" s="36">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" ht="13.55" customHeight="1">
+      <c r="A17" t="s" s="41">
+        <v>20</v>
+      </c>
+      <c r="B17" t="s" s="42">
+        <v>21</v>
+      </c>
+      <c r="C17" t="s" s="42">
+        <v>39</v>
+      </c>
+      <c r="D17" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="E17" s="43">
+        <v>2025</v>
+      </c>
+      <c r="F17" t="s" s="42">
+        <v>40</v>
+      </c>
+      <c r="G17" t="s" s="42">
+        <v>24</v>
+      </c>
+      <c r="H17" t="s" s="42">
+        <v>41</v>
+      </c>
+      <c r="I17" t="s" s="42">
+        <v>49</v>
+      </c>
+      <c r="J17" t="s" s="44">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" ht="13.55" customHeight="1">
+      <c r="A18" t="s" s="31">
+        <v>20</v>
+      </c>
+      <c r="B18" t="s" s="31">
         <v>50</v>
       </c>
-      <c r="B14" t="s" s="38">
+      <c r="C18" t="s" s="31">
         <v>51</v>
       </c>
-      <c r="C14" t="s" s="38">
+      <c r="D18" s="32">
+        <v>0.656</v>
+      </c>
+      <c r="E18" s="32">
+        <v>2025</v>
+      </c>
+      <c r="F18" t="s" s="31">
+        <v>52</v>
+      </c>
+      <c r="G18" t="s" s="31">
+        <v>53</v>
+      </c>
+      <c r="H18" t="s" s="31">
+        <v>54</v>
+      </c>
+      <c r="I18" t="s" s="31">
+        <v>55</v>
+      </c>
+      <c r="J18" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" ht="13.55" customHeight="1">
+      <c r="A19" t="s" s="31">
+        <v>20</v>
+      </c>
+      <c r="B19" t="s" s="31">
+        <v>50</v>
+      </c>
+      <c r="C19" t="s" s="31">
+        <v>36</v>
+      </c>
+      <c r="D19" s="32">
+        <v>0.15</v>
+      </c>
+      <c r="E19" s="32">
+        <v>2025</v>
+      </c>
+      <c r="F19" t="s" s="31">
+        <v>52</v>
+      </c>
+      <c r="G19" t="s" s="31">
+        <v>53</v>
+      </c>
+      <c r="H19" t="s" s="31">
+        <v>54</v>
+      </c>
+      <c r="I19" t="s" s="31">
         <v>56</v>
       </c>
-      <c r="D14" s="39">
-        <v>0.204</v>
-      </c>
-      <c r="E14" s="39">
-        <v>2024</v>
-      </c>
-      <c r="F14" t="s" s="38">
-        <v>52</v>
-      </c>
-      <c r="G14" t="s" s="38">
+      <c r="J19" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" ht="13.55" customHeight="1">
+      <c r="A20" t="s" s="31">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s" s="31">
+        <v>57</v>
+      </c>
+      <c r="C20" t="s" s="31">
+        <v>22</v>
+      </c>
+      <c r="D20" s="32">
+        <v>0.85</v>
+      </c>
+      <c r="E20" s="32">
+        <v>2022</v>
+      </c>
+      <c r="F20" t="s" s="31">
+        <v>58</v>
+      </c>
+      <c r="G20" t="s" s="31">
+        <v>59</v>
+      </c>
+      <c r="H20" t="s" s="31">
+        <v>60</v>
+      </c>
+      <c r="I20" t="s" s="31">
+        <v>61</v>
+      </c>
+      <c r="J20" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" ht="13.55" customHeight="1">
+      <c r="A21" t="s" s="33">
+        <v>62</v>
+      </c>
+      <c r="B21" t="s" s="34">
+        <v>63</v>
+      </c>
+      <c r="C21" t="s" s="34">
+        <v>22</v>
+      </c>
+      <c r="D21" s="35">
+        <v>0.737</v>
+      </c>
+      <c r="E21" s="35">
+        <v>2025</v>
+      </c>
+      <c r="F21" t="s" s="34">
+        <v>64</v>
+      </c>
+      <c r="G21" t="s" s="34">
         <v>53</v>
       </c>
-      <c r="H14" t="s" s="38">
+      <c r="H21" t="s" s="34">
         <v>54</v>
       </c>
-      <c r="I14" t="s" s="40">
-        <v>57</v>
-      </c>
-      <c r="J14" t="s" s="31">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" ht="13.55" customHeight="1">
-      <c r="A15" t="s" s="37">
-        <v>50</v>
-      </c>
-      <c r="B15" t="s" s="38">
-        <v>51</v>
-      </c>
-      <c r="C15" t="s" s="38">
-        <v>58</v>
-      </c>
-      <c r="D15" s="39">
-        <v>0.055</v>
-      </c>
-      <c r="E15" s="39">
-        <v>2024</v>
-      </c>
-      <c r="F15" t="s" s="38">
-        <v>52</v>
-      </c>
-      <c r="G15" t="s" s="38">
-        <v>53</v>
-      </c>
-      <c r="H15" t="s" s="38">
-        <v>54</v>
-      </c>
-      <c r="I15" t="s" s="40">
-        <v>59</v>
-      </c>
-      <c r="J15" t="s" s="31">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" ht="13.55" customHeight="1">
-      <c r="A16" t="s" s="37">
-        <v>50</v>
-      </c>
-      <c r="B16" t="s" s="38">
-        <v>51</v>
-      </c>
-      <c r="C16" t="s" s="38">
-        <v>39</v>
-      </c>
-      <c r="D16" s="39">
-        <v>0.018</v>
-      </c>
-      <c r="E16" s="39">
-        <v>2024</v>
-      </c>
-      <c r="F16" t="s" s="38">
-        <v>52</v>
-      </c>
-      <c r="G16" t="s" s="38">
-        <v>53</v>
-      </c>
-      <c r="H16" t="s" s="38">
-        <v>54</v>
-      </c>
-      <c r="I16" t="s" s="40">
-        <v>60</v>
-      </c>
-      <c r="J16" t="s" s="31">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" ht="13.55" customHeight="1">
-      <c r="A17" t="s" s="37">
-        <v>61</v>
-      </c>
-      <c r="B17" t="s" s="38">
-        <v>62</v>
-      </c>
-      <c r="C17" t="s" s="38">
-        <v>36</v>
-      </c>
-      <c r="D17" s="39">
-        <v>0.429</v>
-      </c>
-      <c r="E17" s="39">
-        <v>2024</v>
-      </c>
-      <c r="F17" t="s" s="38">
-        <v>63</v>
-      </c>
-      <c r="G17" t="s" s="38">
-        <v>53</v>
-      </c>
-      <c r="H17" t="s" s="38">
-        <v>54</v>
-      </c>
-      <c r="I17" t="s" s="40">
-        <v>64</v>
-      </c>
-      <c r="J17" t="s" s="31">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" ht="13.55" customHeight="1">
-      <c r="A18" t="s" s="37">
-        <v>61</v>
-      </c>
-      <c r="B18" t="s" s="38">
-        <v>62</v>
-      </c>
-      <c r="C18" t="s" s="38">
-        <v>22</v>
-      </c>
-      <c r="D18" s="39">
-        <v>0.313</v>
-      </c>
-      <c r="E18" s="39">
-        <v>2024</v>
-      </c>
-      <c r="F18" t="s" s="38">
+      <c r="I21" t="s" s="36">
         <v>65</v>
-      </c>
-      <c r="G18" t="s" s="38">
-        <v>53</v>
-      </c>
-      <c r="H18" t="s" s="38">
-        <v>54</v>
-      </c>
-      <c r="I18" t="s" s="40">
-        <v>66</v>
-      </c>
-      <c r="J18" t="s" s="31">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" ht="13.55" customHeight="1">
-      <c r="A19" t="s" s="37">
-        <v>61</v>
-      </c>
-      <c r="B19" t="s" s="38">
-        <v>62</v>
-      </c>
-      <c r="C19" t="s" s="38">
-        <v>67</v>
-      </c>
-      <c r="D19" s="39">
-        <v>0.036</v>
-      </c>
-      <c r="E19" s="39">
-        <v>2024</v>
-      </c>
-      <c r="F19" t="s" s="38">
-        <v>65</v>
-      </c>
-      <c r="G19" t="s" s="38">
-        <v>53</v>
-      </c>
-      <c r="H19" t="s" s="38">
-        <v>54</v>
-      </c>
-      <c r="I19" t="s" s="40">
-        <v>68</v>
-      </c>
-      <c r="J19" t="s" s="31">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" ht="13.55" customHeight="1">
-      <c r="A20" t="s" s="37">
-        <v>61</v>
-      </c>
-      <c r="B20" t="s" s="38">
-        <v>62</v>
-      </c>
-      <c r="C20" t="s" s="38">
-        <v>30</v>
-      </c>
-      <c r="D20" s="39">
-        <v>0.032</v>
-      </c>
-      <c r="E20" s="39">
-        <v>2024</v>
-      </c>
-      <c r="F20" t="s" s="38">
-        <v>65</v>
-      </c>
-      <c r="G20" t="s" s="38">
-        <v>53</v>
-      </c>
-      <c r="H20" t="s" s="38">
-        <v>54</v>
-      </c>
-      <c r="I20" t="s" s="40">
-        <v>69</v>
-      </c>
-      <c r="J20" t="s" s="31">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" ht="13.55" customHeight="1">
-      <c r="A21" t="s" s="37">
-        <v>61</v>
-      </c>
-      <c r="B21" t="s" s="38">
-        <v>62</v>
-      </c>
-      <c r="C21" t="s" s="38">
-        <v>39</v>
-      </c>
-      <c r="D21" s="39">
-        <v>0.023</v>
-      </c>
-      <c r="E21" s="39">
-        <v>2024</v>
-      </c>
-      <c r="F21" t="s" s="38">
-        <v>65</v>
-      </c>
-      <c r="G21" t="s" s="38">
-        <v>53</v>
-      </c>
-      <c r="H21" t="s" s="38">
-        <v>54</v>
-      </c>
-      <c r="I21" t="s" s="40">
-        <v>70</v>
       </c>
       <c r="J21" t="s" s="31">
         <v>27</v>
@@ -2777,22 +2905,22 @@
     </row>
     <row r="22" ht="13.55" customHeight="1">
       <c r="A22" t="s" s="37">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B22" t="s" s="38">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C22" t="s" s="38">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="D22" s="39">
-        <v>0.018</v>
+        <v>0.163</v>
       </c>
       <c r="E22" s="39">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F22" t="s" s="38">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G22" t="s" s="38">
         <v>53</v>
@@ -2801,7 +2929,7 @@
         <v>54</v>
       </c>
       <c r="I22" t="s" s="40">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="J22" t="s" s="31">
         <v>27</v>
@@ -2809,22 +2937,22 @@
     </row>
     <row r="23" ht="13.55" customHeight="1">
       <c r="A23" t="s" s="37">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B23" t="s" s="38">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="C23" t="s" s="38">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="D23" s="39">
-        <v>0.957</v>
+        <v>0.05</v>
       </c>
       <c r="E23" s="39">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F23" t="s" s="38">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="G23" t="s" s="38">
         <v>53</v>
@@ -2833,7 +2961,7 @@
         <v>54</v>
       </c>
       <c r="I23" t="s" s="40">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="J23" t="s" s="31">
         <v>27</v>
@@ -2841,22 +2969,22 @@
     </row>
     <row r="24" ht="13.55" customHeight="1">
       <c r="A24" t="s" s="37">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B24" t="s" s="38">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="C24" t="s" s="38">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D24" s="39">
-        <v>0.024</v>
+        <v>0.019</v>
       </c>
       <c r="E24" s="39">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F24" t="s" s="38">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="G24" t="s" s="38">
         <v>53</v>
@@ -2865,7 +2993,7 @@
         <v>54</v>
       </c>
       <c r="I24" t="s" s="40">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="J24" t="s" s="31">
         <v>27</v>
@@ -2873,22 +3001,22 @@
     </row>
     <row r="25" ht="13.55" customHeight="1">
       <c r="A25" t="s" s="37">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="B25" t="s" s="38">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="C25" t="s" s="38">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="D25" s="39">
-        <v>0.957</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E25" s="39">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F25" t="s" s="38">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G25" t="s" s="38">
         <v>53</v>
@@ -2896,31 +3024,31 @@
       <c r="H25" t="s" s="38">
         <v>54</v>
       </c>
-      <c r="I25" t="s" s="40">
-        <v>79</v>
-      </c>
-      <c r="J25" t="s" s="31">
+      <c r="I25" t="s" s="38">
+        <v>73</v>
+      </c>
+      <c r="J25" t="s" s="36">
         <v>27</v>
       </c>
     </row>
     <row r="26" ht="13.55" customHeight="1">
       <c r="A26" t="s" s="37">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="B26" t="s" s="38">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="C26" t="s" s="38">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="D26" s="39">
-        <v>0.024</v>
+        <v>0.003</v>
       </c>
       <c r="E26" s="39">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F26" t="s" s="38">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G26" t="s" s="38">
         <v>53</v>
@@ -2928,31 +3056,31 @@
       <c r="H26" t="s" s="38">
         <v>54</v>
       </c>
-      <c r="I26" t="s" s="40">
-        <v>80</v>
-      </c>
-      <c r="J26" t="s" s="31">
+      <c r="I26" t="s" s="38">
+        <v>75</v>
+      </c>
+      <c r="J26" t="s" s="44">
         <v>27</v>
       </c>
     </row>
     <row r="27" ht="13.55" customHeight="1">
       <c r="A27" t="s" s="37">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B27" t="s" s="38">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C27" t="s" s="38">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D27" s="39">
-        <v>0.913</v>
+        <v>0.451</v>
       </c>
       <c r="E27" s="39">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F27" t="s" s="38">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G27" t="s" s="38">
         <v>53</v>
@@ -2961,7 +3089,7 @@
         <v>54</v>
       </c>
       <c r="I27" t="s" s="40">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="J27" t="s" s="31">
         <v>27</v>
@@ -2969,22 +3097,22 @@
     </row>
     <row r="28" ht="13.55" customHeight="1">
       <c r="A28" t="s" s="37">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B28" t="s" s="38">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s" s="38">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="D28" s="39">
-        <v>0.045</v>
+        <v>0.311</v>
       </c>
       <c r="E28" s="39">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F28" t="s" s="38">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="38">
         <v>53</v>
@@ -2993,7 +3121,7 @@
         <v>54</v>
       </c>
       <c r="I28" t="s" s="40">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="J28" t="s" s="31">
         <v>27</v>
@@ -3001,22 +3129,22 @@
     </row>
     <row r="29" ht="13.55" customHeight="1">
       <c r="A29" t="s" s="37">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B29" t="s" s="38">
+        <v>77</v>
+      </c>
+      <c r="C29" t="s" s="38">
         <v>82</v>
       </c>
-      <c r="C29" t="s" s="38">
-        <v>88</v>
-      </c>
       <c r="D29" s="39">
-        <v>0.012</v>
+        <v>0.033</v>
       </c>
       <c r="E29" s="39">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F29" t="s" s="38">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="38">
         <v>53</v>
@@ -3025,7 +3153,7 @@
         <v>54</v>
       </c>
       <c r="I29" t="s" s="40">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="J29" t="s" s="31">
         <v>27</v>
@@ -3033,31 +3161,31 @@
     </row>
     <row r="30" ht="13.55" customHeight="1">
       <c r="A30" t="s" s="37">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="B30" t="s" s="38">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C30" t="s" s="38">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D30" s="39">
-        <v>0.95</v>
+        <v>0.034</v>
       </c>
       <c r="E30" s="39">
         <v>2025</v>
       </c>
       <c r="F30" t="s" s="38">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s" s="38">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="H30" t="s" s="38">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="I30" t="s" s="40">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J30" t="s" s="31">
         <v>27</v>
@@ -3065,31 +3193,31 @@
     </row>
     <row r="31" ht="13.55" customHeight="1">
       <c r="A31" t="s" s="37">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="B31" t="s" s="38">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C31" t="s" s="38">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D31" s="39">
-        <v>0.03</v>
+        <v>0.023</v>
       </c>
       <c r="E31" s="39">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F31" t="s" s="38">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="38">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="H31" t="s" s="38">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="I31" t="s" s="40">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="J31" t="s" s="31">
         <v>27</v>
@@ -3097,31 +3225,31 @@
     </row>
     <row r="32" ht="13.55" customHeight="1">
       <c r="A32" t="s" s="37">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="B32" t="s" s="38">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C32" t="s" s="38">
-        <v>97</v>
+        <v>28</v>
       </c>
       <c r="D32" s="39">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="E32" s="39">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F32" t="s" s="38">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="38">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="H32" t="s" s="38">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="I32" t="s" s="40">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="J32" t="s" s="31">
         <v>27</v>
@@ -3129,31 +3257,31 @@
     </row>
     <row r="33" ht="13.55" customHeight="1">
       <c r="A33" t="s" s="37">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="B33" t="s" s="38">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="C33" t="s" s="38">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D33" s="39">
-        <v>0.7</v>
+        <v>0.029</v>
       </c>
       <c r="E33" s="39">
         <v>2025</v>
       </c>
       <c r="F33" t="s" s="38">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="G33" t="s" s="38">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="H33" t="s" s="38">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="I33" t="s" s="40">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="J33" t="s" s="31">
         <v>27</v>
@@ -3161,31 +3289,31 @@
     </row>
     <row r="34" ht="13.55" customHeight="1">
       <c r="A34" t="s" s="37">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="B34" t="s" s="38">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="C34" t="s" s="38">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="D34" s="39">
-        <v>0.05</v>
+        <v>0.027</v>
       </c>
       <c r="E34" s="39">
         <v>2025</v>
       </c>
       <c r="F34" t="s" s="38">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="G34" t="s" s="38">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="H34" t="s" s="38">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="I34" t="s" s="40">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="J34" t="s" s="31">
         <v>27</v>
@@ -3193,609 +3321,1537 @@
     </row>
     <row r="35" ht="13.55" customHeight="1">
       <c r="A35" t="s" s="37">
+        <v>76</v>
+      </c>
+      <c r="B35" t="s" s="38">
+        <v>77</v>
+      </c>
+      <c r="C35" t="s" s="38">
+        <v>92</v>
+      </c>
+      <c r="D35" s="39">
+        <v>0.017</v>
+      </c>
+      <c r="E35" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F35" t="s" s="38">
+        <v>89</v>
+      </c>
+      <c r="G35" t="s" s="38">
+        <v>53</v>
+      </c>
+      <c r="H35" t="s" s="38">
+        <v>54</v>
+      </c>
+      <c r="I35" t="s" s="40">
+        <v>93</v>
+      </c>
+      <c r="J35" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" ht="26.55" customHeight="1">
+      <c r="A36" t="s" s="37">
+        <v>76</v>
+      </c>
+      <c r="B36" t="s" s="38">
+        <v>94</v>
+      </c>
+      <c r="C36" t="s" s="38">
+        <v>22</v>
+      </c>
+      <c r="D36" s="39">
+        <v>0.75</v>
+      </c>
+      <c r="E36" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F36" t="s" s="38">
+        <v>95</v>
+      </c>
+      <c r="G36" t="s" s="38">
+        <v>96</v>
+      </c>
+      <c r="H36" t="s" s="38">
+        <v>54</v>
+      </c>
+      <c r="I36" t="s" s="38">
+        <v>97</v>
+      </c>
+      <c r="J36" t="s" s="36">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" ht="26.55" customHeight="1">
+      <c r="A37" t="s" s="37">
+        <v>76</v>
+      </c>
+      <c r="B37" t="s" s="38">
+        <v>94</v>
+      </c>
+      <c r="C37" t="s" s="38">
+        <v>36</v>
+      </c>
+      <c r="D37" s="39">
+        <v>0.1</v>
+      </c>
+      <c r="E37" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F37" t="s" s="38">
+        <v>95</v>
+      </c>
+      <c r="G37" t="s" s="38">
+        <v>96</v>
+      </c>
+      <c r="H37" t="s" s="38">
+        <v>54</v>
+      </c>
+      <c r="I37" t="s" s="38">
+        <v>98</v>
+      </c>
+      <c r="J37" t="s" s="44">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" ht="26.55" customHeight="1">
+      <c r="A38" t="s" s="37">
         <v>99</v>
       </c>
-      <c r="B35" t="s" s="38">
+      <c r="B38" t="s" s="38">
         <v>100</v>
       </c>
-      <c r="C35" t="s" s="38">
-        <v>88</v>
-      </c>
-      <c r="D35" s="39">
+      <c r="C38" t="s" s="38">
+        <v>22</v>
+      </c>
+      <c r="D38" s="39">
+        <v>0.944</v>
+      </c>
+      <c r="E38" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F38" t="s" s="38">
+        <v>101</v>
+      </c>
+      <c r="G38" t="s" s="38">
+        <v>53</v>
+      </c>
+      <c r="H38" t="s" s="38">
+        <v>54</v>
+      </c>
+      <c r="I38" t="s" s="40">
+        <v>102</v>
+      </c>
+      <c r="J38" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" ht="26.55" customHeight="1">
+      <c r="A39" t="s" s="37">
+        <v>99</v>
+      </c>
+      <c r="B39" t="s" s="38">
+        <v>100</v>
+      </c>
+      <c r="C39" t="s" s="38">
+        <v>32</v>
+      </c>
+      <c r="D39" s="39">
+        <v>0.03</v>
+      </c>
+      <c r="E39" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F39" t="s" s="38">
+        <v>101</v>
+      </c>
+      <c r="G39" t="s" s="38">
+        <v>53</v>
+      </c>
+      <c r="H39" t="s" s="38">
+        <v>54</v>
+      </c>
+      <c r="I39" t="s" s="40">
+        <v>103</v>
+      </c>
+      <c r="J39" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40" ht="26.55" customHeight="1">
+      <c r="A40" t="s" s="37">
+        <v>99</v>
+      </c>
+      <c r="B40" t="s" s="38">
+        <v>100</v>
+      </c>
+      <c r="C40" t="s" s="38">
+        <v>36</v>
+      </c>
+      <c r="D40" s="39">
+        <v>0.014</v>
+      </c>
+      <c r="E40" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F40" t="s" s="38">
+        <v>104</v>
+      </c>
+      <c r="G40" t="s" s="38">
+        <v>53</v>
+      </c>
+      <c r="H40" t="s" s="38">
+        <v>54</v>
+      </c>
+      <c r="I40" t="s" s="40">
+        <v>105</v>
+      </c>
+      <c r="J40" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" ht="26.55" customHeight="1">
+      <c r="A41" t="s" s="37">
+        <v>99</v>
+      </c>
+      <c r="B41" t="s" s="38">
+        <v>100</v>
+      </c>
+      <c r="C41" t="s" s="38">
+        <v>74</v>
+      </c>
+      <c r="D41" s="39">
+        <v>0.006</v>
+      </c>
+      <c r="E41" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F41" t="s" s="38">
+        <v>104</v>
+      </c>
+      <c r="G41" t="s" s="38">
+        <v>53</v>
+      </c>
+      <c r="H41" t="s" s="38">
+        <v>54</v>
+      </c>
+      <c r="I41" t="s" s="40">
+        <v>106</v>
+      </c>
+      <c r="J41" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" ht="26.55" customHeight="1">
+      <c r="A42" t="s" s="37">
+        <v>99</v>
+      </c>
+      <c r="B42" t="s" s="38">
+        <v>100</v>
+      </c>
+      <c r="C42" t="s" s="38">
+        <v>107</v>
+      </c>
+      <c r="D42" s="39">
+        <v>0.002</v>
+      </c>
+      <c r="E42" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F42" t="s" s="38">
+        <v>104</v>
+      </c>
+      <c r="G42" t="s" s="38">
+        <v>53</v>
+      </c>
+      <c r="H42" t="s" s="38">
+        <v>54</v>
+      </c>
+      <c r="I42" t="s" s="40">
+        <v>108</v>
+      </c>
+      <c r="J42" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43" ht="26.55" customHeight="1">
+      <c r="A43" t="s" s="37">
+        <v>99</v>
+      </c>
+      <c r="B43" t="s" s="38">
+        <v>100</v>
+      </c>
+      <c r="C43" t="s" s="38">
+        <v>71</v>
+      </c>
+      <c r="D43" s="39">
+        <v>0.002</v>
+      </c>
+      <c r="E43" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F43" t="s" s="38">
+        <v>104</v>
+      </c>
+      <c r="G43" t="s" s="38">
+        <v>53</v>
+      </c>
+      <c r="H43" t="s" s="38">
+        <v>54</v>
+      </c>
+      <c r="I43" t="s" s="40">
+        <v>109</v>
+      </c>
+      <c r="J43" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" ht="26.55" customHeight="1">
+      <c r="A44" t="s" s="37">
+        <v>110</v>
+      </c>
+      <c r="B44" t="s" s="38">
+        <v>111</v>
+      </c>
+      <c r="C44" t="s" s="38">
+        <v>22</v>
+      </c>
+      <c r="D44" s="39">
+        <v>0.944</v>
+      </c>
+      <c r="E44" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F44" t="s" s="38">
+        <v>101</v>
+      </c>
+      <c r="G44" t="s" s="38">
+        <v>53</v>
+      </c>
+      <c r="H44" t="s" s="38">
+        <v>54</v>
+      </c>
+      <c r="I44" t="s" s="40">
+        <v>102</v>
+      </c>
+      <c r="J44" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" ht="26.55" customHeight="1">
+      <c r="A45" t="s" s="37">
+        <v>110</v>
+      </c>
+      <c r="B45" t="s" s="38">
+        <v>111</v>
+      </c>
+      <c r="C45" t="s" s="38">
+        <v>32</v>
+      </c>
+      <c r="D45" s="39">
+        <v>0.03</v>
+      </c>
+      <c r="E45" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F45" t="s" s="38">
+        <v>101</v>
+      </c>
+      <c r="G45" t="s" s="38">
+        <v>53</v>
+      </c>
+      <c r="H45" t="s" s="38">
+        <v>54</v>
+      </c>
+      <c r="I45" t="s" s="40">
+        <v>103</v>
+      </c>
+      <c r="J45" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" ht="26.55" customHeight="1">
+      <c r="A46" t="s" s="37">
+        <v>110</v>
+      </c>
+      <c r="B46" t="s" s="38">
+        <v>111</v>
+      </c>
+      <c r="C46" t="s" s="38">
+        <v>36</v>
+      </c>
+      <c r="D46" s="39">
+        <v>0.014</v>
+      </c>
+      <c r="E46" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F46" t="s" s="38">
+        <v>104</v>
+      </c>
+      <c r="G46" t="s" s="38">
+        <v>53</v>
+      </c>
+      <c r="H46" t="s" s="38">
+        <v>54</v>
+      </c>
+      <c r="I46" t="s" s="40">
+        <v>105</v>
+      </c>
+      <c r="J46" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47" ht="26.55" customHeight="1">
+      <c r="A47" t="s" s="37">
+        <v>110</v>
+      </c>
+      <c r="B47" t="s" s="38">
+        <v>111</v>
+      </c>
+      <c r="C47" t="s" s="38">
+        <v>74</v>
+      </c>
+      <c r="D47" s="39">
+        <v>0.006</v>
+      </c>
+      <c r="E47" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F47" t="s" s="38">
+        <v>104</v>
+      </c>
+      <c r="G47" t="s" s="38">
+        <v>53</v>
+      </c>
+      <c r="H47" t="s" s="38">
+        <v>54</v>
+      </c>
+      <c r="I47" t="s" s="40">
+        <v>106</v>
+      </c>
+      <c r="J47" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48" ht="26.55" customHeight="1">
+      <c r="A48" t="s" s="37">
+        <v>110</v>
+      </c>
+      <c r="B48" t="s" s="38">
+        <v>111</v>
+      </c>
+      <c r="C48" t="s" s="38">
+        <v>107</v>
+      </c>
+      <c r="D48" s="39">
+        <v>0.002</v>
+      </c>
+      <c r="E48" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F48" t="s" s="38">
+        <v>104</v>
+      </c>
+      <c r="G48" t="s" s="38">
+        <v>53</v>
+      </c>
+      <c r="H48" t="s" s="38">
+        <v>54</v>
+      </c>
+      <c r="I48" t="s" s="40">
+        <v>108</v>
+      </c>
+      <c r="J48" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49" ht="26.55" customHeight="1">
+      <c r="A49" t="s" s="37">
+        <v>110</v>
+      </c>
+      <c r="B49" t="s" s="38">
+        <v>111</v>
+      </c>
+      <c r="C49" t="s" s="38">
+        <v>71</v>
+      </c>
+      <c r="D49" s="39">
+        <v>0.002</v>
+      </c>
+      <c r="E49" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F49" t="s" s="38">
+        <v>104</v>
+      </c>
+      <c r="G49" t="s" s="38">
+        <v>53</v>
+      </c>
+      <c r="H49" t="s" s="38">
+        <v>54</v>
+      </c>
+      <c r="I49" t="s" s="40">
+        <v>109</v>
+      </c>
+      <c r="J49" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50" ht="26.55" customHeight="1">
+      <c r="A50" t="s" s="37">
+        <v>112</v>
+      </c>
+      <c r="B50" t="s" s="38">
+        <v>113</v>
+      </c>
+      <c r="C50" t="s" s="38">
+        <v>22</v>
+      </c>
+      <c r="D50" s="39">
+        <v>0.843</v>
+      </c>
+      <c r="E50" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F50" t="s" s="38">
+        <v>114</v>
+      </c>
+      <c r="G50" t="s" s="38">
+        <v>53</v>
+      </c>
+      <c r="H50" t="s" s="38">
+        <v>54</v>
+      </c>
+      <c r="I50" t="s" s="40">
+        <v>115</v>
+      </c>
+      <c r="J50" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51" ht="26.55" customHeight="1">
+      <c r="A51" t="s" s="37">
+        <v>112</v>
+      </c>
+      <c r="B51" t="s" s="38">
+        <v>113</v>
+      </c>
+      <c r="C51" t="s" s="38">
+        <v>116</v>
+      </c>
+      <c r="D51" s="39">
+        <v>0.056</v>
+      </c>
+      <c r="E51" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F51" t="s" s="38">
+        <v>117</v>
+      </c>
+      <c r="G51" t="s" s="38">
+        <v>53</v>
+      </c>
+      <c r="H51" t="s" s="38">
+        <v>54</v>
+      </c>
+      <c r="I51" t="s" s="40">
+        <v>118</v>
+      </c>
+      <c r="J51" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="52" ht="26.55" customHeight="1">
+      <c r="A52" t="s" s="37">
+        <v>112</v>
+      </c>
+      <c r="B52" t="s" s="38">
+        <v>113</v>
+      </c>
+      <c r="C52" t="s" s="38">
+        <v>74</v>
+      </c>
+      <c r="D52" s="39">
+        <v>0.056</v>
+      </c>
+      <c r="E52" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F52" t="s" s="38">
+        <v>117</v>
+      </c>
+      <c r="G52" t="s" s="38">
+        <v>53</v>
+      </c>
+      <c r="H52" t="s" s="38">
+        <v>54</v>
+      </c>
+      <c r="I52" t="s" s="40">
+        <v>119</v>
+      </c>
+      <c r="J52" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="53" ht="26.55" customHeight="1">
+      <c r="A53" t="s" s="37">
+        <v>112</v>
+      </c>
+      <c r="B53" t="s" s="38">
+        <v>113</v>
+      </c>
+      <c r="C53" t="s" s="38">
+        <v>120</v>
+      </c>
+      <c r="D53" s="39">
+        <v>0.011</v>
+      </c>
+      <c r="E53" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F53" t="s" s="38">
+        <v>121</v>
+      </c>
+      <c r="G53" t="s" s="38">
+        <v>53</v>
+      </c>
+      <c r="H53" t="s" s="38">
+        <v>54</v>
+      </c>
+      <c r="I53" t="s" s="40">
+        <v>122</v>
+      </c>
+      <c r="J53" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54" ht="13.55" customHeight="1">
+      <c r="A54" t="s" s="37">
+        <v>112</v>
+      </c>
+      <c r="B54" t="s" s="38">
+        <v>113</v>
+      </c>
+      <c r="C54" t="s" s="38">
+        <v>123</v>
+      </c>
+      <c r="D54" s="39">
+        <v>0.011</v>
+      </c>
+      <c r="E54" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F54" t="s" s="38">
+        <v>121</v>
+      </c>
+      <c r="G54" t="s" s="38">
+        <v>53</v>
+      </c>
+      <c r="H54" t="s" s="38">
+        <v>54</v>
+      </c>
+      <c r="I54" t="s" s="40">
+        <v>124</v>
+      </c>
+      <c r="J54" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55" ht="13.55" customHeight="1">
+      <c r="A55" t="s" s="37">
+        <v>112</v>
+      </c>
+      <c r="B55" t="s" s="38">
+        <v>125</v>
+      </c>
+      <c r="C55" t="s" s="38">
+        <v>22</v>
+      </c>
+      <c r="D55" s="39">
+        <v>0.89</v>
+      </c>
+      <c r="E55" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F55" t="s" s="38">
+        <v>126</v>
+      </c>
+      <c r="G55" t="s" s="38">
+        <v>127</v>
+      </c>
+      <c r="H55" t="s" s="38">
+        <v>128</v>
+      </c>
+      <c r="I55" t="s" s="38">
+        <v>129</v>
+      </c>
+      <c r="J55" t="s" s="36">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56" ht="13.55" customHeight="1">
+      <c r="A56" t="s" s="37">
+        <v>112</v>
+      </c>
+      <c r="B56" t="s" s="38">
+        <v>125</v>
+      </c>
+      <c r="C56" t="s" s="38">
+        <v>116</v>
+      </c>
+      <c r="D56" s="39">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E56" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F56" t="s" s="38">
+        <v>126</v>
+      </c>
+      <c r="G56" t="s" s="38">
+        <v>127</v>
+      </c>
+      <c r="H56" t="s" s="38">
+        <v>128</v>
+      </c>
+      <c r="I56" t="s" s="38">
+        <v>130</v>
+      </c>
+      <c r="J56" t="s" s="40">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57" ht="26.55" customHeight="1">
+      <c r="A57" t="s" s="37">
+        <v>112</v>
+      </c>
+      <c r="B57" t="s" s="38">
+        <v>125</v>
+      </c>
+      <c r="C57" t="s" s="38">
+        <v>74</v>
+      </c>
+      <c r="D57" s="39">
+        <v>0.02</v>
+      </c>
+      <c r="E57" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F57" t="s" s="38">
+        <v>126</v>
+      </c>
+      <c r="G57" t="s" s="38">
+        <v>127</v>
+      </c>
+      <c r="H57" t="s" s="38">
+        <v>128</v>
+      </c>
+      <c r="I57" t="s" s="38">
+        <v>131</v>
+      </c>
+      <c r="J57" t="s" s="40">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58" ht="26.55" customHeight="1">
+      <c r="A58" t="s" s="37">
+        <v>112</v>
+      </c>
+      <c r="B58" t="s" s="38">
+        <v>125</v>
+      </c>
+      <c r="C58" t="s" s="38">
+        <v>132</v>
+      </c>
+      <c r="D58" s="39">
+        <v>0.01</v>
+      </c>
+      <c r="E58" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F58" t="s" s="38">
+        <v>126</v>
+      </c>
+      <c r="G58" t="s" s="38">
+        <v>127</v>
+      </c>
+      <c r="H58" t="s" s="38">
+        <v>128</v>
+      </c>
+      <c r="I58" t="s" s="38">
+        <v>133</v>
+      </c>
+      <c r="J58" t="s" s="44">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59" ht="26.55" customHeight="1">
+      <c r="A59" t="s" s="37">
+        <v>134</v>
+      </c>
+      <c r="B59" t="s" s="38">
+        <v>135</v>
+      </c>
+      <c r="C59" t="s" s="38">
+        <v>22</v>
+      </c>
+      <c r="D59" s="39">
+        <v>0.95</v>
+      </c>
+      <c r="E59" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F59" t="s" s="38">
+        <v>136</v>
+      </c>
+      <c r="G59" t="s" s="38">
+        <v>96</v>
+      </c>
+      <c r="H59" t="s" s="38">
+        <v>54</v>
+      </c>
+      <c r="I59" t="s" s="40">
+        <v>137</v>
+      </c>
+      <c r="J59" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60" ht="26.55" customHeight="1">
+      <c r="A60" t="s" s="37">
+        <v>134</v>
+      </c>
+      <c r="B60" t="s" s="38">
+        <v>135</v>
+      </c>
+      <c r="C60" t="s" s="38">
+        <v>32</v>
+      </c>
+      <c r="D60" s="39">
+        <v>0.03</v>
+      </c>
+      <c r="E60" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F60" t="s" s="38">
+        <v>136</v>
+      </c>
+      <c r="G60" t="s" s="38">
+        <v>96</v>
+      </c>
+      <c r="H60" t="s" s="38">
+        <v>54</v>
+      </c>
+      <c r="I60" t="s" s="40">
+        <v>138</v>
+      </c>
+      <c r="J60" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="61" ht="26.55" customHeight="1">
+      <c r="A61" t="s" s="37">
+        <v>134</v>
+      </c>
+      <c r="B61" t="s" s="38">
+        <v>135</v>
+      </c>
+      <c r="C61" t="s" s="38">
+        <v>139</v>
+      </c>
+      <c r="D61" s="39">
+        <v>0.02</v>
+      </c>
+      <c r="E61" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F61" t="s" s="38">
+        <v>136</v>
+      </c>
+      <c r="G61" t="s" s="38">
+        <v>96</v>
+      </c>
+      <c r="H61" t="s" s="38">
+        <v>54</v>
+      </c>
+      <c r="I61" t="s" s="40">
+        <v>140</v>
+      </c>
+      <c r="J61" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="62" ht="26.55" customHeight="1">
+      <c r="A62" t="s" s="37">
+        <v>141</v>
+      </c>
+      <c r="B62" t="s" s="38">
+        <v>142</v>
+      </c>
+      <c r="C62" t="s" s="38">
+        <v>22</v>
+      </c>
+      <c r="D62" s="39">
+        <v>0.7</v>
+      </c>
+      <c r="E62" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F62" t="s" s="38">
+        <v>143</v>
+      </c>
+      <c r="G62" t="s" s="38">
+        <v>96</v>
+      </c>
+      <c r="H62" t="s" s="38">
+        <v>54</v>
+      </c>
+      <c r="I62" t="s" s="40">
+        <v>144</v>
+      </c>
+      <c r="J62" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="63" ht="26.55" customHeight="1">
+      <c r="A63" t="s" s="37">
+        <v>141</v>
+      </c>
+      <c r="B63" t="s" s="38">
+        <v>142</v>
+      </c>
+      <c r="C63" t="s" s="38">
+        <v>145</v>
+      </c>
+      <c r="D63" s="39">
         <v>0.05</v>
       </c>
-      <c r="E35" s="39">
-        <v>2025</v>
-      </c>
-      <c r="F35" t="s" s="38">
-        <v>101</v>
-      </c>
-      <c r="G35" t="s" s="38">
-        <v>93</v>
-      </c>
-      <c r="H35" t="s" s="38">
-        <v>94</v>
-      </c>
-      <c r="I35" t="s" s="40">
-        <v>105</v>
-      </c>
-      <c r="J35" t="s" s="31">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="36" ht="26.55" customHeight="1">
-      <c r="A36" t="s" s="29">
-        <v>106</v>
-      </c>
-      <c r="B36" t="s" s="29">
-        <v>107</v>
-      </c>
-      <c r="C36" t="s" s="29">
+      <c r="E63" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F63" t="s" s="38">
+        <v>143</v>
+      </c>
+      <c r="G63" t="s" s="38">
+        <v>96</v>
+      </c>
+      <c r="H63" t="s" s="38">
+        <v>54</v>
+      </c>
+      <c r="I63" t="s" s="40">
+        <v>146</v>
+      </c>
+      <c r="J63" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="64" ht="26.55" customHeight="1">
+      <c r="A64" t="s" s="37">
+        <v>141</v>
+      </c>
+      <c r="B64" t="s" s="38">
+        <v>142</v>
+      </c>
+      <c r="C64" t="s" s="38">
+        <v>74</v>
+      </c>
+      <c r="D64" s="39">
+        <v>0.05</v>
+      </c>
+      <c r="E64" s="39">
+        <v>2025</v>
+      </c>
+      <c r="F64" t="s" s="38">
+        <v>143</v>
+      </c>
+      <c r="G64" t="s" s="38">
+        <v>96</v>
+      </c>
+      <c r="H64" t="s" s="38">
+        <v>54</v>
+      </c>
+      <c r="I64" t="s" s="40">
+        <v>147</v>
+      </c>
+      <c r="J64" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65" ht="26.55" customHeight="1">
+      <c r="A65" t="s" s="29">
+        <v>148</v>
+      </c>
+      <c r="B65" t="s" s="29">
+        <v>125</v>
+      </c>
+      <c r="C65" t="s" s="29">
         <v>22</v>
       </c>
-      <c r="D36" s="30">
+      <c r="D65" s="30">
         <v>0.89</v>
       </c>
-      <c r="E36" s="30">
-        <v>2025</v>
-      </c>
-      <c r="F36" t="s" s="29">
-        <v>108</v>
-      </c>
-      <c r="G36" t="s" s="29">
-        <v>109</v>
-      </c>
-      <c r="H36" t="s" s="29">
-        <v>110</v>
-      </c>
-      <c r="I36" t="s" s="29">
-        <v>111</v>
-      </c>
-      <c r="J36" t="s" s="31">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="37" ht="26.55" customHeight="1">
-      <c r="A37" t="s" s="31">
-        <v>106</v>
-      </c>
-      <c r="B37" t="s" s="31">
-        <v>107</v>
-      </c>
-      <c r="C37" t="s" s="31">
-        <v>85</v>
-      </c>
-      <c r="D37" s="32">
+      <c r="E65" s="30">
+        <v>2025</v>
+      </c>
+      <c r="F65" t="s" s="29">
+        <v>149</v>
+      </c>
+      <c r="G65" t="s" s="29">
+        <v>127</v>
+      </c>
+      <c r="H65" t="s" s="29">
+        <v>128</v>
+      </c>
+      <c r="I65" t="s" s="29">
+        <v>150</v>
+      </c>
+      <c r="J65" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="66" ht="26.55" customHeight="1">
+      <c r="A66" t="s" s="31">
+        <v>148</v>
+      </c>
+      <c r="B66" t="s" s="31">
+        <v>125</v>
+      </c>
+      <c r="C66" t="s" s="31">
+        <v>116</v>
+      </c>
+      <c r="D66" s="32">
         <v>0.07000000000000001</v>
       </c>
-      <c r="E37" s="32">
-        <v>2025</v>
-      </c>
-      <c r="F37" t="s" s="31">
-        <v>108</v>
-      </c>
-      <c r="G37" t="s" s="31">
-        <v>109</v>
-      </c>
-      <c r="H37" t="s" s="31">
-        <v>110</v>
-      </c>
-      <c r="I37" t="s" s="31">
-        <v>112</v>
-      </c>
-      <c r="J37" t="s" s="31">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="38" ht="26.55" customHeight="1">
-      <c r="A38" t="s" s="31">
-        <v>106</v>
-      </c>
-      <c r="B38" t="s" s="31">
-        <v>107</v>
-      </c>
-      <c r="C38" t="s" s="31">
-        <v>88</v>
-      </c>
-      <c r="D38" s="32">
+      <c r="E66" s="32">
+        <v>2025</v>
+      </c>
+      <c r="F66" t="s" s="31">
+        <v>149</v>
+      </c>
+      <c r="G66" t="s" s="31">
+        <v>127</v>
+      </c>
+      <c r="H66" t="s" s="31">
+        <v>128</v>
+      </c>
+      <c r="I66" t="s" s="31">
+        <v>151</v>
+      </c>
+      <c r="J66" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="67" ht="26.55" customHeight="1">
+      <c r="A67" t="s" s="31">
+        <v>148</v>
+      </c>
+      <c r="B67" t="s" s="31">
+        <v>125</v>
+      </c>
+      <c r="C67" t="s" s="31">
+        <v>74</v>
+      </c>
+      <c r="D67" s="32">
         <v>0.02</v>
       </c>
-      <c r="E38" s="32">
-        <v>2025</v>
-      </c>
-      <c r="F38" t="s" s="31">
-        <v>108</v>
-      </c>
-      <c r="G38" t="s" s="31">
-        <v>109</v>
-      </c>
-      <c r="H38" t="s" s="31">
-        <v>110</v>
-      </c>
-      <c r="I38" t="s" s="31">
-        <v>113</v>
-      </c>
-      <c r="J38" t="s" s="31">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" ht="26.55" customHeight="1">
-      <c r="A39" t="s" s="31">
-        <v>106</v>
-      </c>
-      <c r="B39" t="s" s="31">
-        <v>107</v>
-      </c>
-      <c r="C39" t="s" s="31">
-        <v>114</v>
-      </c>
-      <c r="D39" s="32">
+      <c r="E67" s="32">
+        <v>2025</v>
+      </c>
+      <c r="F67" t="s" s="31">
+        <v>149</v>
+      </c>
+      <c r="G67" t="s" s="31">
+        <v>127</v>
+      </c>
+      <c r="H67" t="s" s="31">
+        <v>128</v>
+      </c>
+      <c r="I67" t="s" s="31">
+        <v>152</v>
+      </c>
+      <c r="J67" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="68" ht="26.55" customHeight="1">
+      <c r="A68" t="s" s="31">
+        <v>148</v>
+      </c>
+      <c r="B68" t="s" s="31">
+        <v>125</v>
+      </c>
+      <c r="C68" t="s" s="31">
+        <v>132</v>
+      </c>
+      <c r="D68" s="32">
         <v>0.01</v>
       </c>
-      <c r="E39" s="32">
-        <v>2025</v>
-      </c>
-      <c r="F39" t="s" s="31">
-        <v>108</v>
-      </c>
-      <c r="G39" t="s" s="31">
-        <v>109</v>
-      </c>
-      <c r="H39" t="s" s="31">
-        <v>110</v>
-      </c>
-      <c r="I39" t="s" s="31">
-        <v>115</v>
-      </c>
-      <c r="J39" t="s" s="31">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="40" ht="26.55" customHeight="1">
-      <c r="A40" t="s" s="31">
+      <c r="E68" s="32">
+        <v>2025</v>
+      </c>
+      <c r="F68" t="s" s="31">
+        <v>149</v>
+      </c>
+      <c r="G68" t="s" s="31">
+        <v>127</v>
+      </c>
+      <c r="H68" t="s" s="31">
+        <v>128</v>
+      </c>
+      <c r="I68" t="s" s="31">
+        <v>153</v>
+      </c>
+      <c r="J68" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="69" ht="26.55" customHeight="1">
+      <c r="A69" t="s" s="31">
+        <v>154</v>
+      </c>
+      <c r="B69" t="s" s="31">
+        <v>125</v>
+      </c>
+      <c r="C69" t="s" s="31">
+        <v>22</v>
+      </c>
+      <c r="D69" s="32">
+        <v>0.89</v>
+      </c>
+      <c r="E69" s="32">
+        <v>2025</v>
+      </c>
+      <c r="F69" t="s" s="31">
+        <v>149</v>
+      </c>
+      <c r="G69" t="s" s="31">
+        <v>127</v>
+      </c>
+      <c r="H69" t="s" s="31">
+        <v>128</v>
+      </c>
+      <c r="I69" t="s" s="31">
+        <v>150</v>
+      </c>
+      <c r="J69" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="70" ht="26.55" customHeight="1">
+      <c r="A70" t="s" s="31">
+        <v>154</v>
+      </c>
+      <c r="B70" t="s" s="31">
+        <v>125</v>
+      </c>
+      <c r="C70" t="s" s="31">
         <v>116</v>
       </c>
-      <c r="B40" t="s" s="31">
-        <v>107</v>
-      </c>
-      <c r="C40" t="s" s="31">
+      <c r="D70" s="32">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E70" s="32">
+        <v>2025</v>
+      </c>
+      <c r="F70" t="s" s="31">
+        <v>149</v>
+      </c>
+      <c r="G70" t="s" s="31">
+        <v>127</v>
+      </c>
+      <c r="H70" t="s" s="31">
+        <v>128</v>
+      </c>
+      <c r="I70" t="s" s="31">
+        <v>151</v>
+      </c>
+      <c r="J70" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="71" ht="26.55" customHeight="1">
+      <c r="A71" t="s" s="31">
+        <v>154</v>
+      </c>
+      <c r="B71" t="s" s="31">
+        <v>125</v>
+      </c>
+      <c r="C71" t="s" s="31">
+        <v>74</v>
+      </c>
+      <c r="D71" s="32">
+        <v>0.02</v>
+      </c>
+      <c r="E71" s="32">
+        <v>2025</v>
+      </c>
+      <c r="F71" t="s" s="31">
+        <v>149</v>
+      </c>
+      <c r="G71" t="s" s="31">
+        <v>127</v>
+      </c>
+      <c r="H71" t="s" s="31">
+        <v>128</v>
+      </c>
+      <c r="I71" t="s" s="31">
+        <v>152</v>
+      </c>
+      <c r="J71" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="72" ht="26.55" customHeight="1">
+      <c r="A72" t="s" s="31">
+        <v>154</v>
+      </c>
+      <c r="B72" t="s" s="31">
+        <v>125</v>
+      </c>
+      <c r="C72" t="s" s="31">
+        <v>132</v>
+      </c>
+      <c r="D72" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="E72" s="32">
+        <v>2025</v>
+      </c>
+      <c r="F72" t="s" s="31">
+        <v>149</v>
+      </c>
+      <c r="G72" t="s" s="31">
+        <v>127</v>
+      </c>
+      <c r="H72" t="s" s="31">
+        <v>128</v>
+      </c>
+      <c r="I72" t="s" s="31">
+        <v>153</v>
+      </c>
+      <c r="J72" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="73" ht="26.55" customHeight="1">
+      <c r="A73" t="s" s="31">
+        <v>155</v>
+      </c>
+      <c r="B73" t="s" s="31">
+        <v>125</v>
+      </c>
+      <c r="C73" t="s" s="31">
         <v>22</v>
       </c>
-      <c r="D40" s="32">
-        <v>0.89</v>
-      </c>
-      <c r="E40" s="32">
-        <v>2025</v>
-      </c>
-      <c r="F40" t="s" s="31">
-        <v>108</v>
-      </c>
-      <c r="G40" t="s" s="31">
-        <v>109</v>
-      </c>
-      <c r="H40" t="s" s="31">
-        <v>110</v>
-      </c>
-      <c r="I40" t="s" s="31">
-        <v>111</v>
-      </c>
-      <c r="J40" t="s" s="31">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="41" ht="26.55" customHeight="1">
-      <c r="A41" t="s" s="31">
+      <c r="D73" s="32">
+        <v>0.98</v>
+      </c>
+      <c r="E73" s="32">
+        <v>2025</v>
+      </c>
+      <c r="F73" t="s" s="31">
+        <v>156</v>
+      </c>
+      <c r="G73" t="s" s="31">
+        <v>157</v>
+      </c>
+      <c r="H73" t="s" s="31">
+        <v>158</v>
+      </c>
+      <c r="I73" t="s" s="31">
+        <v>159</v>
+      </c>
+      <c r="J73" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="74" ht="26.55" customHeight="1">
+      <c r="A74" t="s" s="31">
+        <v>155</v>
+      </c>
+      <c r="B74" t="s" s="31">
+        <v>125</v>
+      </c>
+      <c r="C74" t="s" s="31">
         <v>116</v>
       </c>
-      <c r="B41" t="s" s="31">
-        <v>107</v>
-      </c>
-      <c r="C41" t="s" s="31">
-        <v>85</v>
-      </c>
-      <c r="D41" s="32">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E41" s="32">
-        <v>2025</v>
-      </c>
-      <c r="F41" t="s" s="31">
-        <v>108</v>
-      </c>
-      <c r="G41" t="s" s="31">
-        <v>109</v>
-      </c>
-      <c r="H41" t="s" s="31">
-        <v>110</v>
-      </c>
-      <c r="I41" t="s" s="31">
-        <v>112</v>
-      </c>
-      <c r="J41" t="s" s="31">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="42" ht="26.55" customHeight="1">
-      <c r="A42" t="s" s="31">
+      <c r="D74" s="32">
+        <v>0.02</v>
+      </c>
+      <c r="E74" s="32">
+        <v>2025</v>
+      </c>
+      <c r="F74" t="s" s="31">
+        <v>156</v>
+      </c>
+      <c r="G74" t="s" s="31">
+        <v>157</v>
+      </c>
+      <c r="H74" t="s" s="31">
+        <v>158</v>
+      </c>
+      <c r="I74" t="s" s="31">
+        <v>160</v>
+      </c>
+      <c r="J74" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="75" ht="26.55" customHeight="1">
+      <c r="A75" t="s" s="31">
+        <v>161</v>
+      </c>
+      <c r="B75" t="s" s="31">
+        <v>125</v>
+      </c>
+      <c r="C75" t="s" s="31">
+        <v>22</v>
+      </c>
+      <c r="D75" s="32">
+        <v>0.98</v>
+      </c>
+      <c r="E75" s="32">
+        <v>2025</v>
+      </c>
+      <c r="F75" t="s" s="31">
+        <v>156</v>
+      </c>
+      <c r="G75" t="s" s="31">
+        <v>157</v>
+      </c>
+      <c r="H75" t="s" s="31">
+        <v>158</v>
+      </c>
+      <c r="I75" t="s" s="31">
+        <v>159</v>
+      </c>
+      <c r="J75" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="76" ht="26.55" customHeight="1">
+      <c r="A76" t="s" s="31">
+        <v>161</v>
+      </c>
+      <c r="B76" t="s" s="31">
+        <v>125</v>
+      </c>
+      <c r="C76" t="s" s="31">
         <v>116</v>
       </c>
-      <c r="B42" t="s" s="31">
-        <v>107</v>
-      </c>
-      <c r="C42" t="s" s="31">
-        <v>88</v>
-      </c>
-      <c r="D42" s="32">
+      <c r="D76" s="32">
         <v>0.02</v>
       </c>
-      <c r="E42" s="32">
-        <v>2025</v>
-      </c>
-      <c r="F42" t="s" s="31">
-        <v>108</v>
-      </c>
-      <c r="G42" t="s" s="31">
-        <v>109</v>
-      </c>
-      <c r="H42" t="s" s="31">
-        <v>110</v>
-      </c>
-      <c r="I42" t="s" s="31">
-        <v>113</v>
-      </c>
-      <c r="J42" t="s" s="31">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="43" ht="26.55" customHeight="1">
-      <c r="A43" t="s" s="31">
-        <v>116</v>
-      </c>
-      <c r="B43" t="s" s="31">
-        <v>107</v>
-      </c>
-      <c r="C43" t="s" s="31">
-        <v>114</v>
-      </c>
-      <c r="D43" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="E43" s="32">
-        <v>2025</v>
-      </c>
-      <c r="F43" t="s" s="31">
-        <v>108</v>
-      </c>
-      <c r="G43" t="s" s="31">
-        <v>109</v>
-      </c>
-      <c r="H43" t="s" s="31">
-        <v>110</v>
-      </c>
-      <c r="I43" t="s" s="31">
-        <v>115</v>
-      </c>
-      <c r="J43" t="s" s="31">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="44" ht="26.55" customHeight="1">
-      <c r="A44" t="s" s="31">
-        <v>117</v>
-      </c>
-      <c r="B44" t="s" s="31">
-        <v>107</v>
-      </c>
-      <c r="C44" t="s" s="31">
+      <c r="E76" s="32">
+        <v>2025</v>
+      </c>
+      <c r="F76" t="s" s="31">
+        <v>156</v>
+      </c>
+      <c r="G76" t="s" s="31">
+        <v>157</v>
+      </c>
+      <c r="H76" t="s" s="31">
+        <v>158</v>
+      </c>
+      <c r="I76" t="s" s="31">
+        <v>160</v>
+      </c>
+      <c r="J76" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="77" ht="26.55" customHeight="1">
+      <c r="A77" t="s" s="31">
+        <v>162</v>
+      </c>
+      <c r="B77" t="s" s="31">
+        <v>163</v>
+      </c>
+      <c r="C77" t="s" s="31">
         <v>22</v>
       </c>
-      <c r="D44" s="32">
-        <v>0.98</v>
-      </c>
-      <c r="E44" s="32">
-        <v>2025</v>
-      </c>
-      <c r="F44" t="s" s="31">
-        <v>118</v>
-      </c>
-      <c r="G44" t="s" s="31">
-        <v>119</v>
-      </c>
-      <c r="H44" t="s" s="31">
-        <v>120</v>
-      </c>
-      <c r="I44" t="s" s="31">
-        <v>121</v>
-      </c>
-      <c r="J44" t="s" s="31">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="45" ht="26.55" customHeight="1">
-      <c r="A45" t="s" s="31">
-        <v>117</v>
-      </c>
-      <c r="B45" t="s" s="31">
-        <v>107</v>
-      </c>
-      <c r="C45" t="s" s="31">
-        <v>85</v>
-      </c>
-      <c r="D45" s="32">
-        <v>0.02</v>
-      </c>
-      <c r="E45" s="32">
-        <v>2025</v>
-      </c>
-      <c r="F45" t="s" s="31">
-        <v>118</v>
-      </c>
-      <c r="G45" t="s" s="31">
-        <v>119</v>
-      </c>
-      <c r="H45" t="s" s="31">
-        <v>120</v>
-      </c>
-      <c r="I45" t="s" s="31">
-        <v>122</v>
-      </c>
-      <c r="J45" t="s" s="31">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="46" ht="26.55" customHeight="1">
-      <c r="A46" t="s" s="31">
-        <v>123</v>
-      </c>
-      <c r="B46" t="s" s="31">
-        <v>107</v>
-      </c>
-      <c r="C46" t="s" s="31">
-        <v>22</v>
-      </c>
-      <c r="D46" s="32">
-        <v>0.98</v>
-      </c>
-      <c r="E46" s="32">
-        <v>2025</v>
-      </c>
-      <c r="F46" t="s" s="31">
-        <v>118</v>
-      </c>
-      <c r="G46" t="s" s="31">
-        <v>119</v>
-      </c>
-      <c r="H46" t="s" s="31">
-        <v>120</v>
-      </c>
-      <c r="I46" t="s" s="31">
-        <v>121</v>
-      </c>
-      <c r="J46" t="s" s="31">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="47" ht="26.55" customHeight="1">
-      <c r="A47" t="s" s="31">
-        <v>123</v>
-      </c>
-      <c r="B47" t="s" s="31">
-        <v>107</v>
-      </c>
-      <c r="C47" t="s" s="31">
-        <v>85</v>
-      </c>
-      <c r="D47" s="32">
-        <v>0.02</v>
-      </c>
-      <c r="E47" s="32">
-        <v>2025</v>
-      </c>
-      <c r="F47" t="s" s="31">
-        <v>118</v>
-      </c>
-      <c r="G47" t="s" s="31">
-        <v>119</v>
-      </c>
-      <c r="H47" t="s" s="31">
-        <v>120</v>
-      </c>
-      <c r="I47" t="s" s="31">
-        <v>122</v>
-      </c>
-      <c r="J47" t="s" s="31">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="48" ht="26.55" customHeight="1">
-      <c r="A48" t="s" s="31">
-        <v>124</v>
-      </c>
-      <c r="B48" t="s" s="31">
-        <v>125</v>
-      </c>
-      <c r="C48" t="s" s="31">
-        <v>22</v>
-      </c>
-      <c r="D48" s="32">
+      <c r="D77" s="32">
         <v>0.68</v>
       </c>
-      <c r="E48" s="32">
-        <v>2025</v>
-      </c>
-      <c r="F48" t="s" s="31">
-        <v>126</v>
-      </c>
-      <c r="G48" t="s" s="31">
-        <v>127</v>
-      </c>
-      <c r="H48" t="s" s="31">
-        <v>128</v>
-      </c>
-      <c r="I48" t="s" s="31">
-        <v>129</v>
-      </c>
-      <c r="J48" t="s" s="31">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="49" ht="26.55" customHeight="1">
-      <c r="A49" t="s" s="31">
-        <v>124</v>
-      </c>
-      <c r="B49" t="s" s="31">
-        <v>125</v>
-      </c>
-      <c r="C49" t="s" s="31">
+      <c r="E77" s="32">
+        <v>2025</v>
+      </c>
+      <c r="F77" t="s" s="31">
+        <v>164</v>
+      </c>
+      <c r="G77" t="s" s="31">
+        <v>165</v>
+      </c>
+      <c r="H77" t="s" s="31">
+        <v>166</v>
+      </c>
+      <c r="I77" t="s" s="31">
+        <v>167</v>
+      </c>
+      <c r="J77" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="78" ht="26.55" customHeight="1">
+      <c r="A78" t="s" s="31">
+        <v>162</v>
+      </c>
+      <c r="B78" t="s" s="31">
+        <v>163</v>
+      </c>
+      <c r="C78" t="s" s="31">
         <v>30</v>
       </c>
-      <c r="D49" s="32">
+      <c r="D78" s="32">
         <v>0.1</v>
       </c>
-      <c r="E49" s="32">
-        <v>2025</v>
-      </c>
-      <c r="F49" t="s" s="31">
-        <v>126</v>
-      </c>
-      <c r="G49" t="s" s="31">
-        <v>127</v>
-      </c>
-      <c r="H49" t="s" s="31">
-        <v>128</v>
-      </c>
-      <c r="I49" t="s" s="31">
-        <v>130</v>
-      </c>
-      <c r="J49" t="s" s="31">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="50" ht="26.55" customHeight="1">
-      <c r="A50" t="s" s="31">
-        <v>124</v>
-      </c>
-      <c r="B50" t="s" s="31">
-        <v>125</v>
-      </c>
-      <c r="C50" t="s" s="31">
-        <v>67</v>
-      </c>
-      <c r="D50" s="32">
+      <c r="E78" s="32">
+        <v>2025</v>
+      </c>
+      <c r="F78" t="s" s="31">
+        <v>164</v>
+      </c>
+      <c r="G78" t="s" s="31">
+        <v>165</v>
+      </c>
+      <c r="H78" t="s" s="31">
+        <v>166</v>
+      </c>
+      <c r="I78" t="s" s="31">
+        <v>168</v>
+      </c>
+      <c r="J78" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="79" ht="26.55" customHeight="1">
+      <c r="A79" t="s" s="31">
+        <v>162</v>
+      </c>
+      <c r="B79" t="s" s="31">
+        <v>163</v>
+      </c>
+      <c r="C79" t="s" s="31">
+        <v>82</v>
+      </c>
+      <c r="D79" s="32">
         <v>0.06</v>
       </c>
-      <c r="E50" s="32">
-        <v>2025</v>
-      </c>
-      <c r="F50" t="s" s="31">
-        <v>126</v>
-      </c>
-      <c r="G50" t="s" s="31">
-        <v>127</v>
-      </c>
-      <c r="H50" t="s" s="31">
-        <v>128</v>
-      </c>
-      <c r="I50" t="s" s="31">
-        <v>131</v>
-      </c>
-      <c r="J50" t="s" s="31">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="51" ht="26.55" customHeight="1">
-      <c r="A51" t="s" s="31">
-        <v>124</v>
-      </c>
-      <c r="B51" t="s" s="31">
-        <v>125</v>
-      </c>
-      <c r="C51" t="s" s="31">
-        <v>97</v>
-      </c>
-      <c r="D51" s="32">
+      <c r="E79" s="32">
+        <v>2025</v>
+      </c>
+      <c r="F79" t="s" s="31">
+        <v>164</v>
+      </c>
+      <c r="G79" t="s" s="31">
+        <v>165</v>
+      </c>
+      <c r="H79" t="s" s="31">
+        <v>166</v>
+      </c>
+      <c r="I79" t="s" s="31">
+        <v>169</v>
+      </c>
+      <c r="J79" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="80" ht="26.55" customHeight="1">
+      <c r="A80" t="s" s="31">
+        <v>162</v>
+      </c>
+      <c r="B80" t="s" s="31">
+        <v>163</v>
+      </c>
+      <c r="C80" t="s" s="31">
+        <v>139</v>
+      </c>
+      <c r="D80" s="32">
         <v>0.06</v>
       </c>
-      <c r="E51" s="32">
-        <v>2025</v>
-      </c>
-      <c r="F51" t="s" s="31">
-        <v>126</v>
-      </c>
-      <c r="G51" t="s" s="31">
-        <v>127</v>
-      </c>
-      <c r="H51" t="s" s="31">
-        <v>128</v>
-      </c>
-      <c r="I51" t="s" s="31">
-        <v>132</v>
-      </c>
-      <c r="J51" t="s" s="31">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="52" ht="26.55" customHeight="1">
-      <c r="A52" t="s" s="31">
-        <v>124</v>
-      </c>
-      <c r="B52" t="s" s="31">
-        <v>125</v>
-      </c>
-      <c r="C52" t="s" s="31">
-        <v>133</v>
-      </c>
-      <c r="D52" s="32">
+      <c r="E80" s="32">
+        <v>2025</v>
+      </c>
+      <c r="F80" t="s" s="31">
+        <v>164</v>
+      </c>
+      <c r="G80" t="s" s="31">
+        <v>165</v>
+      </c>
+      <c r="H80" t="s" s="31">
+        <v>166</v>
+      </c>
+      <c r="I80" t="s" s="31">
+        <v>170</v>
+      </c>
+      <c r="J80" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="81" ht="26.55" customHeight="1">
+      <c r="A81" t="s" s="31">
+        <v>162</v>
+      </c>
+      <c r="B81" t="s" s="31">
+        <v>163</v>
+      </c>
+      <c r="C81" t="s" s="31">
+        <v>71</v>
+      </c>
+      <c r="D81" s="32">
         <v>0.05</v>
       </c>
-      <c r="E52" s="32">
-        <v>2025</v>
-      </c>
-      <c r="F52" t="s" s="31">
-        <v>126</v>
-      </c>
-      <c r="G52" t="s" s="31">
-        <v>127</v>
-      </c>
-      <c r="H52" t="s" s="31">
-        <v>128</v>
-      </c>
-      <c r="I52" t="s" s="31">
-        <v>131</v>
-      </c>
-      <c r="J52" t="s" s="31">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="53" ht="26.55" customHeight="1">
-      <c r="A53" t="s" s="31">
-        <v>124</v>
-      </c>
-      <c r="B53" t="s" s="31">
-        <v>125</v>
-      </c>
-      <c r="C53" t="s" s="31">
-        <v>88</v>
-      </c>
-      <c r="D53" s="32">
+      <c r="E81" s="32">
+        <v>2025</v>
+      </c>
+      <c r="F81" t="s" s="31">
+        <v>164</v>
+      </c>
+      <c r="G81" t="s" s="31">
+        <v>165</v>
+      </c>
+      <c r="H81" t="s" s="31">
+        <v>166</v>
+      </c>
+      <c r="I81" t="s" s="31">
+        <v>169</v>
+      </c>
+      <c r="J81" t="s" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="82" ht="26.55" customHeight="1">
+      <c r="A82" t="s" s="31">
+        <v>162</v>
+      </c>
+      <c r="B82" t="s" s="31">
+        <v>163</v>
+      </c>
+      <c r="C82" t="s" s="31">
+        <v>74</v>
+      </c>
+      <c r="D82" s="32">
         <v>0.05</v>
       </c>
-      <c r="E53" s="32">
-        <v>2025</v>
-      </c>
-      <c r="F53" t="s" s="31">
-        <v>126</v>
-      </c>
-      <c r="G53" t="s" s="31">
-        <v>127</v>
-      </c>
-      <c r="H53" t="s" s="31">
-        <v>128</v>
-      </c>
-      <c r="I53" t="s" s="31">
-        <v>131</v>
-      </c>
-      <c r="J53" t="s" s="31">
+      <c r="E82" s="32">
+        <v>2025</v>
+      </c>
+      <c r="F82" t="s" s="31">
+        <v>164</v>
+      </c>
+      <c r="G82" t="s" s="31">
+        <v>165</v>
+      </c>
+      <c r="H82" t="s" s="31">
+        <v>166</v>
+      </c>
+      <c r="I82" t="s" s="31">
+        <v>169</v>
+      </c>
+      <c r="J82" t="s" s="31">
         <v>27</v>
       </c>
     </row>
@@ -3813,236 +4869,236 @@
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="22" style="41" customWidth="1"/>
-    <col min="2" max="2" width="100" style="41" customWidth="1"/>
-    <col min="3" max="5" width="8.85156" style="41" customWidth="1"/>
-    <col min="6" max="16384" width="8.85156" style="41" customWidth="1"/>
+    <col min="1" max="1" width="22" style="45" customWidth="1"/>
+    <col min="2" max="2" width="100" style="45" customWidth="1"/>
+    <col min="3" max="5" width="8.85156" style="45" customWidth="1"/>
+    <col min="6" max="16384" width="8.85156" style="45" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="39.55" customHeight="1">
-      <c r="A1" t="s" s="42">
-        <v>134</v>
+      <c r="A1" t="s" s="46">
+        <v>171</v>
       </c>
       <c r="B1" t="s" s="31">
-        <v>135</v>
-      </c>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
+        <v>172</v>
+      </c>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
     </row>
     <row r="2" ht="13.55" customHeight="1">
-      <c r="A2" s="43"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
     </row>
     <row r="3" ht="52.55" customHeight="1">
-      <c r="A3" t="s" s="42">
-        <v>136</v>
+      <c r="A3" t="s" s="46">
+        <v>173</v>
       </c>
       <c r="B3" t="s" s="31">
-        <v>137</v>
-      </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
+        <v>174</v>
+      </c>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
     </row>
     <row r="4" ht="13.55" customHeight="1">
-      <c r="A4" s="43"/>
-      <c r="B4" s="44"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
+      <c r="A4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
     </row>
     <row r="5" ht="26.55" customHeight="1">
-      <c r="A5" t="s" s="42">
-        <v>138</v>
+      <c r="A5" t="s" s="46">
+        <v>175</v>
       </c>
       <c r="B5" t="s" s="31">
-        <v>139</v>
-      </c>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
+        <v>176</v>
+      </c>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
     </row>
     <row r="6" ht="13.55" customHeight="1">
-      <c r="A6" s="43"/>
-      <c r="B6" s="44"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
+      <c r="A6" s="47"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
     </row>
     <row r="7" ht="13.55" customHeight="1">
-      <c r="A7" t="s" s="42">
+      <c r="A7" t="s" s="46">
         <v>10</v>
       </c>
       <c r="B7" t="s" s="31">
-        <v>140</v>
-      </c>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="43"/>
+        <v>177</v>
+      </c>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="47"/>
     </row>
     <row r="8" ht="26.55" customHeight="1">
-      <c r="A8" t="s" s="42">
+      <c r="A8" t="s" s="46">
         <v>11</v>
       </c>
       <c r="B8" t="s" s="31">
-        <v>141</v>
-      </c>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
+        <v>178</v>
+      </c>
+      <c r="C8" s="47"/>
+      <c r="D8" s="47"/>
+      <c r="E8" s="47"/>
     </row>
     <row r="9" ht="13.55" customHeight="1">
-      <c r="A9" t="s" s="42">
+      <c r="A9" t="s" s="46">
         <v>12</v>
       </c>
       <c r="B9" t="s" s="31">
-        <v>142</v>
-      </c>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
+        <v>179</v>
+      </c>
+      <c r="C9" s="47"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="47"/>
     </row>
     <row r="10" ht="26.55" customHeight="1">
-      <c r="A10" t="s" s="42">
+      <c r="A10" t="s" s="46">
         <v>13</v>
       </c>
       <c r="B10" t="s" s="31">
-        <v>143</v>
-      </c>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
+        <v>180</v>
+      </c>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="47"/>
     </row>
     <row r="11" ht="26.55" customHeight="1">
-      <c r="A11" t="s" s="42">
+      <c r="A11" t="s" s="46">
         <v>14</v>
       </c>
       <c r="B11" t="s" s="31">
-        <v>144</v>
-      </c>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
+        <v>181</v>
+      </c>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
     </row>
     <row r="12" ht="13.55" customHeight="1">
-      <c r="A12" t="s" s="42">
+      <c r="A12" t="s" s="46">
         <v>15</v>
       </c>
       <c r="B12" t="s" s="31">
-        <v>145</v>
-      </c>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
+        <v>182</v>
+      </c>
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
     </row>
     <row r="13" ht="26.55" customHeight="1">
-      <c r="A13" t="s" s="42">
-        <v>146</v>
+      <c r="A13" t="s" s="46">
+        <v>183</v>
       </c>
       <c r="B13" t="s" s="31">
-        <v>147</v>
-      </c>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
+        <v>184</v>
+      </c>
+      <c r="C13" s="47"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
     </row>
     <row r="14" ht="13.55" customHeight="1">
-      <c r="A14" t="s" s="42">
+      <c r="A14" t="s" s="46">
         <v>18</v>
       </c>
       <c r="B14" t="s" s="31">
-        <v>148</v>
-      </c>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
+        <v>185</v>
+      </c>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
     </row>
     <row r="15" ht="13.55" customHeight="1">
-      <c r="A15" t="s" s="42">
+      <c r="A15" t="s" s="46">
         <v>19</v>
       </c>
       <c r="B15" t="s" s="31">
-        <v>149</v>
-      </c>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
+        <v>186</v>
+      </c>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
     </row>
     <row r="16" ht="13.55" customHeight="1">
-      <c r="A16" s="43"/>
-      <c r="B16" s="44"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
+      <c r="A16" s="47"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
     </row>
     <row r="17" ht="26.55" customHeight="1">
-      <c r="A17" t="s" s="42">
-        <v>150</v>
+      <c r="A17" t="s" s="46">
+        <v>187</v>
       </c>
       <c r="B17" t="s" s="31">
-        <v>151</v>
-      </c>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
+        <v>188</v>
+      </c>
+      <c r="C17" s="47"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
     </row>
     <row r="18" ht="13.55" customHeight="1">
-      <c r="A18" s="43"/>
-      <c r="B18" s="44"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
+      <c r="A18" s="47"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
     </row>
     <row r="19" ht="65.55" customHeight="1">
-      <c r="A19" t="s" s="42">
-        <v>152</v>
+      <c r="A19" t="s" s="46">
+        <v>189</v>
       </c>
       <c r="B19" t="s" s="31">
-        <v>153</v>
-      </c>
-      <c r="C19" s="43"/>
-      <c r="D19" s="43"/>
-      <c r="E19" s="43"/>
+        <v>190</v>
+      </c>
+      <c r="C19" s="47"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
     </row>
     <row r="20" ht="13.55" customHeight="1">
-      <c r="A20" s="43"/>
-      <c r="B20" s="44"/>
-      <c r="C20" s="43"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
+      <c r="A20" s="47"/>
+      <c r="B20" s="48"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
     </row>
     <row r="21" ht="26.55" customHeight="1">
-      <c r="A21" t="s" s="42">
-        <v>154</v>
+      <c r="A21" t="s" s="46">
+        <v>191</v>
       </c>
       <c r="B21" t="s" s="31">
-        <v>155</v>
-      </c>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
+        <v>192</v>
+      </c>
+      <c r="C21" s="47"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
     </row>
     <row r="22" ht="13.55" customHeight="1">
-      <c r="A22" s="43"/>
-      <c r="B22" s="44"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
+      <c r="A22" s="47"/>
+      <c r="B22" s="48"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
     </row>
     <row r="23" ht="26.55" customHeight="1">
-      <c r="A23" t="s" s="42">
-        <v>156</v>
+      <c r="A23" t="s" s="46">
+        <v>193</v>
       </c>
       <c r="B23" t="s" s="31">
-        <v>157</v>
-      </c>
-      <c r="C23" s="43"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="43"/>
+        <v>194</v>
+      </c>
+      <c r="C23" s="47"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="47"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
